--- a/Strömungslehre 2/images/SL2-Diagrams.xlsx
+++ b/Strömungslehre 2/images/SL2-Diagrams.xlsx
@@ -1,52 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Phillip\Documents\Git\Project-FoSa\Strömungslehre 2\images\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{304DC812-88D8-45BA-92DD-D95F088E256C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E570561-F534-4684-9540-3A1EFD6A82F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="46296" windowHeight="18696" xr2:uid="{FA5394E7-ED4E-4AC0-A8BA-0A137B0856E0}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="46296" windowHeight="18696" activeTab="3" xr2:uid="{FA5394E7-ED4E-4AC0-A8BA-0A137B0856E0}"/>
   </bookViews>
   <sheets>
     <sheet name="Adiabate-Vorgänge" sheetId="4" r:id="rId1"/>
     <sheet name="xliv" sheetId="1" r:id="rId2"/>
     <sheet name="xlv" sheetId="3" r:id="rId3"/>
+    <sheet name="xlvi" sheetId="5" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">'Adiabate-Vorgänge'!$B$4:$B$34</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">'Adiabate-Vorgänge'!$C$3</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">'Adiabate-Vorgänge'!$G$4:$G$34</definedName>
-    <definedName name="_xlchart.v1.11" hidden="1">'Adiabate-Vorgänge'!$B$4:$B$34</definedName>
-    <definedName name="_xlchart.v1.12" hidden="1">'Adiabate-Vorgänge'!$C$3</definedName>
-    <definedName name="_xlchart.v1.13" hidden="1">'Adiabate-Vorgänge'!$C$4:$C$34</definedName>
-    <definedName name="_xlchart.v1.14" hidden="1">'Adiabate-Vorgänge'!$D$3</definedName>
-    <definedName name="_xlchart.v1.15" hidden="1">'Adiabate-Vorgänge'!$D$4:$D$34</definedName>
-    <definedName name="_xlchart.v1.16" hidden="1">'Adiabate-Vorgänge'!$E$3</definedName>
-    <definedName name="_xlchart.v1.17" hidden="1">'Adiabate-Vorgänge'!$E$4:$E$34</definedName>
-    <definedName name="_xlchart.v1.18" hidden="1">'Adiabate-Vorgänge'!$F$3</definedName>
-    <definedName name="_xlchart.v1.19" hidden="1">'Adiabate-Vorgänge'!$F$4:$F$34</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">'Adiabate-Vorgänge'!$C$4:$C$34</definedName>
-    <definedName name="_xlchart.v1.20" hidden="1">'Adiabate-Vorgänge'!$G$3</definedName>
-    <definedName name="_xlchart.v1.21" hidden="1">'Adiabate-Vorgänge'!$G$4:$G$34</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">'Adiabate-Vorgänge'!$D$3</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">'Adiabate-Vorgänge'!$D$4:$D$34</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">'Adiabate-Vorgänge'!$E$3</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">'Adiabate-Vorgänge'!$E$4:$E$34</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">'Adiabate-Vorgänge'!$F$3</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">'Adiabate-Vorgänge'!$F$4:$F$34</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">'Adiabate-Vorgänge'!$G$3</definedName>
     <definedName name="solver_eng" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_eng" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_num" localSheetId="2" hidden="1">0</definedName>
+    <definedName name="solver_num" localSheetId="3" hidden="1">0</definedName>
     <definedName name="solver_opt" localSheetId="2" hidden="1">xlv!$D$5</definedName>
+    <definedName name="solver_opt" localSheetId="3" hidden="1">xlvi!#REF!</definedName>
     <definedName name="solver_typ" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_typ" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_val" localSheetId="2" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="3" hidden="1">0</definedName>
     <definedName name="solver_ver" localSheetId="2" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="3" hidden="1">3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -69,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="13">
   <si>
     <t>DEG</t>
   </si>
@@ -128,19 +114,23 @@
   <si>
     <t>Verhältnis</t>
   </si>
+  <si>
+    <t>Druckverh.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="&quot;Ma = &quot;0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="&quot;θ = &quot;0&quot;°&quot;"/>
     <numFmt numFmtId="167" formatCode="&quot;= &quot;0.000&quot; RAD&quot;"/>
     <numFmt numFmtId="168" formatCode="0.0000"/>
+    <numFmt numFmtId="169" formatCode="&quot;→ σ = &quot;0.000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -164,8 +154,18 @@
       <color theme="0"/>
       <name val="CMU Serif"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1" tint="0.499984740745262"/>
+      <name val="CMU Serif"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="CMU Serif"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -184,8 +184,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -289,11 +295,63 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -325,6 +383,44 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -351,6 +447,30 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2005,7 +2125,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="15875" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
@@ -2329,7 +2449,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="15875" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
@@ -2653,7 +2773,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="15875" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
@@ -2977,7 +3097,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="15875" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
@@ -3301,7 +3421,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="15875" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
@@ -3625,7 +3745,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="15875" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
@@ -3949,7 +4069,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="15875" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
@@ -4273,7 +4393,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="15875" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
@@ -4597,7 +4717,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="15875" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
@@ -4921,7 +5041,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="15875" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
@@ -5245,7 +5365,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="15875" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
@@ -5569,7 +5689,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="15875" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
@@ -5893,7 +6013,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="15875" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
@@ -6217,7 +6337,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="15875" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
@@ -6541,7 +6661,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="15875" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
@@ -6865,7 +6985,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="15875" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
@@ -7189,7 +7309,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="15875" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
@@ -7513,7 +7633,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="15875" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
@@ -7837,7 +7957,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="15875" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
@@ -8217,56 +8337,13 @@
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                   </a:rPr>
-                  <a:t>Diagramm xliv                                           Stoßwinkel </a:t>
+                  <a:t>Diagramm xliv                                           </a:t>
                 </a:r>
-                <a:r>
-                  <a:rPr lang="de-DE" i="1">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>σ  </a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="de-DE" i="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>[</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="de-DE" sz="500" i="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t> </a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="de-DE" i="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>°</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="de-DE" sz="500" i="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t> </a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="de-DE" i="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>]</a:t>
-                </a:r>
+                <a:endParaRPr lang="de-DE" i="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:endParaRPr>
               </a:p>
             </c:rich>
           </c:tx>
@@ -8380,120 +8457,6 @@
             <a:effectLst/>
           </c:spPr>
         </c:minorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
-                    <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
-                    <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="de-DE">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>Umlenkungswinkel </a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="de-DE" sz="1000" b="0" i="1" u="none" strike="noStrike" baseline="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>θ  </a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="de-DE" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>[</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="de-DE" sz="500" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t> </a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="de-DE" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>°</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="de-DE" sz="500" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t> </a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="de-DE" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>]</a:t>
-                </a:r>
-                <a:endParaRPr lang="de-DE" i="0">
-                  <a:solidFill>
-                    <a:sysClr val="windowText" lastClr="000000"/>
-                  </a:solidFill>
-                </a:endParaRPr>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:layout>
-            <c:manualLayout>
-              <c:xMode val="edge"/>
-              <c:yMode val="edge"/>
-              <c:x val="1.8075322162344625E-2"/>
-              <c:y val="0.42511999726696609"/>
-            </c:manualLayout>
-          </c:layout>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:sysClr val="windowText" lastClr="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
-                  <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
-                  <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="de-DE"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
         <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -8628,7 +8591,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="15875" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent3"/>
               </a:solidFill>
@@ -9021,7 +8984,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="15875" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent3"/>
               </a:solidFill>
@@ -9405,7 +9368,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="15875" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent3"/>
               </a:solidFill>
@@ -9768,7 +9731,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="15875" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent3"/>
               </a:solidFill>
@@ -10095,7 +10058,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="15875" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent3"/>
               </a:solidFill>
@@ -10407,7 +10370,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="15875" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent3"/>
               </a:solidFill>
@@ -10710,7 +10673,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="15875" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent3"/>
               </a:solidFill>
@@ -11001,7 +10964,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="15875" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent3"/>
               </a:solidFill>
@@ -11501,115 +11464,6 @@
             <a:effectLst/>
           </c:spPr>
         </c:minorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
-                    <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
-                    <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="de-DE">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>Stoßwinkel </a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="de-DE" i="1">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>σ  </a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="de-DE" i="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>[</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="de-DE" sz="500" i="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t> </a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="de-DE" i="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>°</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="de-DE" sz="500" i="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t> </a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="de-DE" i="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>]</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:layout>
-            <c:manualLayout>
-              <c:xMode val="edge"/>
-              <c:yMode val="edge"/>
-              <c:x val="1.6142644618641643E-2"/>
-              <c:y val="0.44895602691197822"/>
-            </c:manualLayout>
-          </c:layout>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:sysClr val="windowText" lastClr="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
-                  <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
-                  <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="de-DE"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
         <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -11700,6 +11554,2111 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="de-DE"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.11401724072483124"/>
+          <c:y val="1.4263741923879563E-2"/>
+          <c:w val="0.8602328428767283"/>
+          <c:h val="0.92613323210196863"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>xlvi!$C$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>θ = 0°</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="15875" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>xlvi!$B$6:$B$56</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="51"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.05</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.1000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.1499999999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.25</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.35</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.45</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.55</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.6</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.65</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.7</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.75</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.8</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.85</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.9</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1.95</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2.0499999999999998</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2.1</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2.15</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2.2000000000000002</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2.25</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2.2999999999999998</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2.35</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2.4</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2.4500000000000002</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2.5499999999999998</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2.6</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2.65</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2.7</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2.75</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>2.8</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>2.85</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>2.9</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>2.95</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>3.05</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>3.1</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>3.15</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>3.2</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>3.25</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>3.3</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>3.35</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>3.4</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>3.45</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>3.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>xlvi!$C$6:$C$56</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="51"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.99985299009517314</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.99892801531447117</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.99668975878988608</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.99279839769936207</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.98705677037193806</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.97937364894321854</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.96973709318744861</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.95819441491554602</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.94483668541179422</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.92978651228282927</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.91318827243034917</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.89520026046533652</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.87598837652705697</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.85572107902379757</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.83456539208449942</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.81268379959868853</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.79023188655348287</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.76735660925323457</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.74419509207184276</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.72087386148474575</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.69750843932096973</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.67420322706305214</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.65105162192761434</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.62813631354919564</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.60552971744757467</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.58329450812554562</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.56148422064455572</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.54014389488089332</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.51931074139979472</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.49901481202915121</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.47927966180462583</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.4601229920348951</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.44155726684386321</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.4235902977319202</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.4062257925068673</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.38946386641192116</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.37330151446622861</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.35773304497254471</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.34275047487402643</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.32834388819073695</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.3145017591661417</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.30121124203081562</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.28845842946759725</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.27622858195917344</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.26450633023243536</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.25327585299801569</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.24252103213017481</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.23222558735142332</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.22237319238607181</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.2129475744338053</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-15DF-4DDA-8898-9A5D68691E96}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>xlvi!$E$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>θ = 5°</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="15875" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>xlvi!$D$6:$D$74</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="69"/>
+                <c:pt idx="2">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.6</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.24</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.4</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.6</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.7</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.8</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.9</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2.1</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2.2000000000000002</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2.2999999999999998</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2.4</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2.6</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2.7</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2.8</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2.9</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>3.1</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>3.2</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>3.3</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>3.4</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>3.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>xlvi!$E$6:$E$74</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="69"/>
+                <c:pt idx="2">
+                  <c:v>0.99199999999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.99199999999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.99480000000000002</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.997</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.99860000000000004</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.99909999999999999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.99860000000000004</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.99529999999999996</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.98199999999999998</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.96099999999999997</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.93097323536631904</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.89668953855954769</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.85748419479104809</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.81468275132784285</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.76954852360491333</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.72321447596145572</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.67664948152984683</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.63064814286359361</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.58583596022247098</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.54268371015872352</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.50152659551146428</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.46258509546384113</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.42598550959557474</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.39177898764171454</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.3599584090233614</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.33047286769050638</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.3032397706324319</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.27815470942422532</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.25509934359305275</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.23394756592546659</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.21457022062792372</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000009-15DF-4DDA-8898-9A5D68691E96}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>xlvi!$G$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>θ = 10°</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="15875" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>xlvi!$F$6:$F$56</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="51"/>
+                <c:pt idx="2">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.6</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.47</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.42</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.6</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.7</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.8</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.9</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.1</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.2000000000000002</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.2999999999999998</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2.4</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2.6</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2.7</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2.8</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2.9</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>3.1</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>3.2</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>3.3</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>3.4</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>3.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>xlvi!$G$6:$G$56</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="51"/>
+                <c:pt idx="2">
+                  <c:v>0.94699999999999995</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.96299999999999997</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.97599999999999998</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.98509999999999998</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.98719999999999997</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.98839999999999995</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.98670000000000002</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.97499999999999998</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.94299999999999995</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.90639999999999998</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.86599999999999999</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.82199999999999995</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.77271704449629175</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.72660209482121385</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.68019385655875653</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.63429111067139099</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.5895251960035558</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.54637360468298235</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.50517853734810947</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.46616732721433957</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.4294726999735734</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.39515163240801376</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.36320214652323718</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.33357777092578467</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.30619965817406303</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.2809665020476706</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.25776248190390483</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.23646349585475601</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.21694194788937024</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000A-15DF-4DDA-8898-9A5D68691E96}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>xlvi!$I$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>θ = 15°</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="15875" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>xlvi!$H$6:$H$56</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="51"/>
+                <c:pt idx="3">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.25</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.68</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.615</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.65</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.7</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.8</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.9</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.1</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.2000000000000002</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.2999999999999998</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2.4</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2.6</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2.7</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2.8</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2.9</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>3.1</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>3.2</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>3.3</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>3.4</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>3.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>xlvi!$I$6:$I$56</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="51"/>
+                <c:pt idx="3">
+                  <c:v>0.85299999999999998</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.89549999999999996</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.92900000000000005</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.9425</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.95299999999999996</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.95730000000000004</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.95499999999999996</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.94</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.90900000000000003</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.88300000000000001</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.83499999999999996</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.78600000000000003</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.73699999999999999</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.68899999999999995</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.63954414111559987</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.59485187765508241</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.55170761073228358</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.51046350829404075</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.471356720670987</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.43452921921018928</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.4000463970508964</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.36791373024646179</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.33809119695554091</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.31050541521127234</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.28505962089186293</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.2616416961413689</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.2401304976683529</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.22040074148669114</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000C-15DF-4DDA-8898-9A5D68691E96}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>xlvi!$K$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>θ = 20°</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="15875" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dPt>
+            <c:idx val="16"/>
+            <c:marker>
+              <c:symbol val="none"/>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:ln w="15875" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-3391-4A54-B148-221C4E4D2299}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:xVal>
+            <c:numRef>
+              <c:f>xlvi!$J$6:$J$56</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="51"/>
+                <c:pt idx="5">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.2999999999999998</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.2000000000000002</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.1</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.875</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.8380000000000001</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.9</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.1</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.2000000000000002</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.2999999999999998</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2.4</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2.6</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2.7</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2.8</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2.9</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>3.1</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>3.2</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>3.3</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>3.4</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>3.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>xlvi!$K$6:$K$56</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="51"/>
+                <c:pt idx="5">
+                  <c:v>0.72799999999999998</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.79700000000000004</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.85499999999999998</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.874</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.88200000000000001</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.88900000000000001</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.89280000000000004</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.89</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.86899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.81299999999999994</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.75600000000000001</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.70199999999999996</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.65100000000000002</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.60299999999999998</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.55679831860296347</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.51551387521716441</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.47632163636926</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.43937234568894878</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.40473941800707208</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.37243546307410436</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.34242665539444356</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.31464488394076012</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.28899778205713644</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.26537683152192743</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.24366377826453306</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.22373560792157701</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3391-4A54-B148-221C4E4D2299}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>xlvi!$M$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>θ = 25°</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="15875" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>xlvi!$L$6:$L$56</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="51"/>
+                <c:pt idx="7">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.8</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.4</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.2999999999999998</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.21</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.1259999999999999</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.15</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.2000000000000002</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.2999999999999998</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2.4</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2.6</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2.7</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2.8</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2.9</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>3.1</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>3.2</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>3.3</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>3.4</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>3.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>xlvi!$M$6:$M$56</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="51"/>
+                <c:pt idx="7">
+                  <c:v>0.59150000000000003</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.66149999999999998</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.71199999999999997</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.75649999999999995</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.76880000000000004</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.77900000000000003</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.78300000000000003</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.77800000000000002</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.75900000000000001</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.72199999999999998</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.68600000000000005</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.627</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.57599999999999996</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.52900000000000003</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.48599999999999999</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.44700000000000001</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.41033107953838149</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.37782859158380155</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.34760260361838224</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.31959132110282829</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.29370766877237847</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.26984747848186424</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.24789600420801144</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.22773300220591197</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-A2FD-485D-972B-17E40096D1D1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>xlvi!$O$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>θ = 30°</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="15875" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>xlvi!$N$6:$N$56</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="51"/>
+                <c:pt idx="13">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3.3</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3.1</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.9</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.7</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.5649999999999999</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2.516</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2.5499999999999998</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2.6</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2.7</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2.8</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2.9</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>3.1</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>3.2</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>3.3</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>3.4</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>3.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>xlvi!$O$6:$O$56</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="51"/>
+                <c:pt idx="13">
+                  <c:v>0.46500000000000002</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.53700000000000003</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.57250000000000001</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.60299999999999998</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.61199999999999999</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.59350000000000003</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.55400000000000005</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.52200000000000002</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.47199999999999998</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.42899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.39100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.35730000000000001</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.32749282829008969</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.30124032311619603</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.27700556840957719</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.25467954157828859</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.23414655206576382</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-A2FD-485D-972B-17E40096D1D1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>xlvi!$Q$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>θ = 35°</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="15875" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>xlvi!$P$6:$P$56</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="51"/>
+                <c:pt idx="22">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>3.3</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>3.18</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>3.1379999999999999</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>3.15</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>3.2</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>3.3</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>3.4</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>3.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>xlvi!$Q$6:$Q$56</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="51"/>
+                <c:pt idx="22">
+                  <c:v>0.34599999999999997</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.372</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.3805</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.373</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.35699999999999998</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.33200000000000002</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.29799999999999999</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.27</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.24627140920000326</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-A2FD-485D-972B-17E40096D1D1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1903764384"/>
+        <c:axId val="1903764864"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1903764384"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="3.5"/>
+          <c:min val="1"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                    <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                    <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="de-DE">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Diagramm xlvi                                                    Ma</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="de-DE" baseline="-25000">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>1</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="de-DE" i="1">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>  </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="de-DE" i="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>[</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="de-DE" sz="500" i="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t> </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="de-DE" i="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>-</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="de-DE" sz="500" i="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t> </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="de-DE" i="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>]</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="2.1526300317190154E-2"/>
+              <c:y val="0.96747213521891962"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                  <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                  <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="de-DE"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1903764864"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="0.2"/>
+        <c:minorUnit val="5.000000000000001E-2"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1903764864"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1"/>
+          <c:min val="0.2"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="65000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1903764384"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="2.0000000000000004E-2"/>
+        <c:minorUnit val="1.0000000000000002E-2"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="rnd" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="bg1">
+          <a:lumMod val="65000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+          <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+          <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="de-DE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.7" r="0.7" t="0.78740157499999996" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -11781,6 +13740,46 @@
 </file>
 
 <file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -13368,6 +15367,522 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -13396,8 +15911,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="6375347" y="198783"/>
-          <a:ext cx="5028811" cy="6560998"/>
+          <a:off x="6415103" y="198783"/>
+          <a:ext cx="5028812" cy="6560998"/>
           <a:chOff x="6388788" y="200297"/>
           <a:chExt cx="5012909" cy="6610978"/>
         </a:xfrm>
@@ -15205,10 +17720,10 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="25" name="Gruppieren 24">
+        <xdr:cNvPr id="14" name="Gruppieren 13">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1691AF5A-CF7F-984B-E3EA-AF92397D3597}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A40A5DE6-4D39-6A91-F910-C2B84F10D99C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -15216,10 +17731,10 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="24319744" y="197653"/>
+          <a:off x="24755172" y="197653"/>
           <a:ext cx="6617456" cy="9598123"/>
           <a:chOff x="24319744" y="197653"/>
-          <a:chExt cx="6356199" cy="9598123"/>
+          <a:chExt cx="6617456" cy="9598123"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:graphicFrame macro="">
@@ -15235,7 +17750,7 @@
         </xdr:nvGraphicFramePr>
         <xdr:xfrm>
           <a:off x="24319744" y="197653"/>
-          <a:ext cx="6356199" cy="9598123"/>
+          <a:ext cx="6617456" cy="9598123"/>
         </xdr:xfrm>
         <a:graphic>
           <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -15256,8 +17771,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="28696513" y="846952"/>
-            <a:ext cx="902235" cy="305078"/>
+            <a:off x="28875302" y="848027"/>
+            <a:ext cx="939025" cy="307367"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -15335,8 +17850,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="28931581" y="1085342"/>
-            <a:ext cx="413466" cy="302239"/>
+            <a:off x="29121566" y="1087254"/>
+            <a:ext cx="429328" cy="300112"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -15392,8 +17907,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="28872996" y="1667556"/>
-            <a:ext cx="413466" cy="302239"/>
+            <a:off x="29058555" y="1669084"/>
+            <a:ext cx="431506" cy="300112"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -15449,8 +17964,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="28834896" y="2073729"/>
-            <a:ext cx="413466" cy="302238"/>
+            <a:off x="29018994" y="2075394"/>
+            <a:ext cx="431506" cy="300109"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -15506,8 +18021,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="28787271" y="2928938"/>
-            <a:ext cx="413466" cy="302239"/>
+            <a:off x="28969542" y="2931808"/>
+            <a:ext cx="431506" cy="300112"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -15563,8 +18078,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="28749171" y="3861027"/>
-            <a:ext cx="413466" cy="302239"/>
+            <a:off x="28929980" y="3862422"/>
+            <a:ext cx="431506" cy="300112"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -15620,8 +18135,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="28744411" y="4104595"/>
-            <a:ext cx="413466" cy="302239"/>
+            <a:off x="28925038" y="4106939"/>
+            <a:ext cx="431506" cy="300112"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -15677,8 +18192,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="28744408" y="4339318"/>
-            <a:ext cx="413466" cy="306321"/>
+            <a:off x="28925034" y="4338066"/>
+            <a:ext cx="431506" cy="308637"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -15734,8 +18249,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="28744408" y="4601937"/>
-            <a:ext cx="413466" cy="302238"/>
+            <a:off x="28925034" y="4602049"/>
+            <a:ext cx="431506" cy="300109"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -15791,8 +18306,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="28734883" y="4898572"/>
-            <a:ext cx="413466" cy="306321"/>
+            <a:off x="28915144" y="4900790"/>
+            <a:ext cx="431506" cy="304281"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -15848,8 +18363,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="28744408" y="5213577"/>
-            <a:ext cx="413466" cy="302239"/>
+            <a:off x="28925034" y="5213944"/>
+            <a:ext cx="431506" cy="300112"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -15905,8 +18420,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="28753525" y="5556069"/>
-            <a:ext cx="413466" cy="306593"/>
+            <a:off x="28934501" y="5555186"/>
+            <a:ext cx="431506" cy="308915"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -15962,8 +18477,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="28766588" y="5934892"/>
-            <a:ext cx="413466" cy="306593"/>
+            <a:off x="28948065" y="5933550"/>
+            <a:ext cx="431506" cy="308915"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -16019,8 +18534,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="28805777" y="6361611"/>
-            <a:ext cx="413466" cy="302239"/>
+            <a:off x="28988758" y="6360852"/>
+            <a:ext cx="431506" cy="304466"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -16076,8 +18591,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="28853675" y="6814457"/>
-            <a:ext cx="413466" cy="302239"/>
+            <a:off x="29038493" y="6814851"/>
+            <a:ext cx="431506" cy="300112"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -16133,8 +18648,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="28927698" y="7280367"/>
-            <a:ext cx="413466" cy="306593"/>
+            <a:off x="29117534" y="7277844"/>
+            <a:ext cx="429328" cy="308915"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -16190,8 +18705,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="29023492" y="7768045"/>
-            <a:ext cx="413466" cy="302239"/>
+            <a:off x="29217003" y="7767432"/>
+            <a:ext cx="429328" cy="300112"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -16247,8 +18762,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="29182424" y="8260080"/>
-            <a:ext cx="411288" cy="306593"/>
+            <a:off x="29382032" y="8257119"/>
+            <a:ext cx="427066" cy="308915"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -16304,8 +18819,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="29443681" y="8699864"/>
-            <a:ext cx="411288" cy="306593"/>
+            <a:off x="29653311" y="8697772"/>
+            <a:ext cx="429243" cy="308915"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -16348,6 +18863,252 @@
           </a:p>
         </xdr:txBody>
       </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="2" name="Textfeld 1">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{213B55D1-97D5-4921-A462-465C8A92DC70}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm rot="16200000">
+            <a:off x="23577677" y="4847104"/>
+            <a:ext cx="1858806" cy="307109"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="de-DE" sz="1100">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t>Umlenkungswinkel </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="el-GR" sz="1100" i="1">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Latin Modern Math" panose="02000503000000000000" pitchFamily="50" charset="0"/>
+                <a:ea typeface="Latin Modern Math" panose="02000503000000000000" pitchFamily="50" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t>ϑ</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="el-GR" sz="1100">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t>  [</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="el-GR" sz="500">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t> </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="el-GR" sz="1100">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t>°</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="el-GR" sz="500">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t> </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="el-GR" sz="1100">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t>]</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="4" name="Textfeld 3">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A2C3E56-D550-4246-856E-7BAE3938DFF3}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="26955200" y="9429991"/>
+            <a:ext cx="1301553" cy="303027"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="de-DE" sz="1100">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t>Stoßwinkel </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="el-GR" sz="1100" i="1">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Latin Modern Math" panose="02000503000000000000" pitchFamily="50" charset="0"/>
+                <a:ea typeface="Latin Modern Math" panose="02000503000000000000" pitchFamily="50" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t>σ</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="el-GR" sz="1100">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t>  [</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="el-GR" sz="500">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t> </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="el-GR" sz="1100">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t>°</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="el-GR" sz="500">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t> </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="el-GR" sz="1100">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t>]</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -16366,15 +19127,15 @@
     <xdr:to>
       <xdr:col>20</xdr:col>
       <xdr:colOff>261257</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>6626</xdr:rowOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="30" name="Gruppieren 29">
+        <xdr:cNvPr id="4" name="Gruppieren 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{916AA565-B63F-583E-2B3E-EF8F610B12AF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E903D2C-539B-5386-6E36-2DE5C5381F23}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -16382,10 +19143,10 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9091270" y="198934"/>
-          <a:ext cx="6571352" cy="9471645"/>
+          <a:off x="9253915" y="197653"/>
+          <a:ext cx="6617456" cy="9599490"/>
           <a:chOff x="9158310" y="200493"/>
-          <a:chExt cx="6621243" cy="9737077"/>
+          <a:chExt cx="6621243" cy="9738637"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:graphicFrame macro="">
@@ -16401,7 +19162,7 @@
         </xdr:nvGraphicFramePr>
         <xdr:xfrm>
           <a:off x="9158310" y="200493"/>
-          <a:ext cx="6621243" cy="9737077"/>
+          <a:ext cx="6621243" cy="9738637"/>
         </xdr:xfrm>
         <a:graphic>
           <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -16421,9 +19182,9 @@
           <xdr:cNvSpPr txBox="1"/>
         </xdr:nvSpPr>
         <xdr:spPr>
-          <a:xfrm rot="2481165">
-            <a:off x="10926419" y="6970644"/>
-            <a:ext cx="1921565" cy="306637"/>
+          <a:xfrm rot="2108448">
+            <a:off x="11274989" y="7274765"/>
+            <a:ext cx="1922649" cy="306268"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -16475,15 +19236,15 @@
               <a:t> </a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="de-DE" sz="1100" i="1" baseline="0">
+              <a:rPr lang="el-GR" sz="1100" i="1" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="accent3"/>
                 </a:solidFill>
-                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
-                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:latin typeface="Latin Modern Math" panose="02000503000000000000" pitchFamily="50" charset="0"/>
+                <a:ea typeface="Latin Modern Math" panose="02000503000000000000" pitchFamily="50" charset="0"/>
                 <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
               </a:rPr>
-              <a:t>θ</a:t>
+              <a:t>ϑ</a:t>
             </a:r>
             <a:r>
               <a:rPr lang="de-DE" sz="1100" baseline="0">
@@ -16520,8 +19281,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="12503427" y="6771861"/>
-            <a:ext cx="344555" cy="306637"/>
+            <a:off x="12503360" y="6772978"/>
+            <a:ext cx="343889" cy="307182"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -16585,8 +19346,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="12695583" y="6407426"/>
-            <a:ext cx="457199" cy="306637"/>
+            <a:off x="12695145" y="6408635"/>
+            <a:ext cx="457914" cy="307183"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -16650,8 +19411,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="12947375" y="5976731"/>
-            <a:ext cx="457199" cy="306637"/>
+            <a:off x="12946450" y="5977718"/>
+            <a:ext cx="457914" cy="307183"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -16715,8 +19476,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="13258802" y="5486401"/>
-            <a:ext cx="457199" cy="306637"/>
+            <a:off x="13258875" y="5487796"/>
+            <a:ext cx="456315" cy="306269"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -16764,6 +19525,129 @@
               <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
               <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
             </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="2" name="Textfeld 1">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B436804-7C9B-4733-A9ED-D7D3FDFD3EBE}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm rot="16200000">
+            <a:off x="8391273" y="4919990"/>
+            <a:ext cx="1908711" cy="308096"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="de-DE" sz="1100">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t>Stoßwinkel </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="el-GR" sz="1100" i="1">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Latin Modern Math" panose="02000503000000000000" pitchFamily="50" charset="0"/>
+                <a:ea typeface="Latin Modern Math" panose="02000503000000000000" pitchFamily="50" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t>σ</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="el-GR" sz="1100">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t>  [</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="el-GR" sz="500">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t> </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="el-GR" sz="1100">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t>°</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="el-GR" sz="500">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t> </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="el-GR" sz="1100">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t>]</a:t>
+            </a:r>
           </a:p>
         </xdr:txBody>
       </xdr:sp>
@@ -17417,15 +20301,15 @@
         <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="de-DE" sz="1100" i="1" baseline="0">
+            <a:rPr lang="el-GR" sz="1100" i="1" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="accent3"/>
               </a:solidFill>
-              <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
-              <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              <a:latin typeface="Latin Modern Math" panose="02000503000000000000" pitchFamily="50" charset="0"/>
+              <a:ea typeface="Latin Modern Math" panose="02000503000000000000" pitchFamily="50" charset="0"/>
               <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
             </a:rPr>
-            <a:t>θ</a:t>
+            <a:t>ϑ</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="de-DE" sz="1100" i="0" baseline="-25000">
@@ -17465,6 +20349,1738 @@
     </cdr:sp>
   </cdr:relSizeAnchor>
 </c:userShapes>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>102121</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>194607</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>519950</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>192897</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="21" name="Gruppieren 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{843A669F-6D8B-A413-88E7-032B16793365}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="15485556" y="194607"/>
+          <a:ext cx="6908276" cy="9724996"/>
+          <a:chOff x="15552947" y="194607"/>
+          <a:chExt cx="6701970" cy="9785020"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:graphicFrame macro="">
+        <xdr:nvGraphicFramePr>
+          <xdr:cNvPr id="3" name="Diagramm 2">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{094CF861-8D14-3B0B-9E74-3821F8A688AE}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGraphicFramePr/>
+        </xdr:nvGraphicFramePr>
+        <xdr:xfrm>
+          <a:off x="15638311" y="194607"/>
+          <a:ext cx="6616606" cy="9785020"/>
+        </xdr:xfrm>
+        <a:graphic>
+          <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+            <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          </a:graphicData>
+        </a:graphic>
+      </xdr:graphicFrame>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="6" name="Textfeld 5">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{260A97A5-92C7-4005-923A-D68283719B86}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm rot="16200000">
+            <a:off x="14715453" y="4952634"/>
+            <a:ext cx="2268002" cy="307920"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="de-DE" sz="1100">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t>Ruhedruckverhältnis      </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="el-GR" sz="1100">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t>  [</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="el-GR" sz="500">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t> </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="de-DE" sz="1100">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t>-</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="el-GR" sz="500">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t> </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="el-GR" sz="1100">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t>]</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="10" name="Gruppieren 9">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94E9F43D-E0DE-38DF-7342-28FDACE616A7}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm rot="16200000">
+            <a:off x="15559900" y="4293101"/>
+            <a:ext cx="554971" cy="568877"/>
+            <a:chOff x="17084177" y="6440727"/>
+            <a:chExt cx="558019" cy="566227"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="7" name="Textfeld 6">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C7E56601-707C-4181-9B00-24C1D666D6F9}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="17084177" y="6440727"/>
+              <a:ext cx="558019" cy="566227"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525" cmpd="sng">
+              <a:noFill/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr lang="de-DE" sz="1100" i="1">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                  <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                  <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                </a:rPr>
+                <a:t>p</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="de-DE" sz="1100" baseline="-25000">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                  <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                  <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                </a:rPr>
+                <a:t>02</a:t>
+              </a:r>
+            </a:p>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr lang="de-DE" sz="1100" i="1">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                  <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                  <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                </a:rPr>
+                <a:t>p</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="de-DE" sz="1100" baseline="-25000">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                  <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                  <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                </a:rPr>
+                <a:t>01</a:t>
+              </a:r>
+              <a:endParaRPr lang="el-GR" sz="1100" baseline="-25000">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="9" name="Gerader Verbinder 8">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{074B2973-0A09-2B34-8D3B-1E54BD86E284}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr/>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="17254726" y="6745158"/>
+              <a:ext cx="231648" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="line">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="6350">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+      </xdr:grpSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="11" name="Textfeld 24">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C102ABB-440E-2254-61DF-C7121013D782}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="20719011" y="5528451"/>
+            <a:ext cx="456935" cy="302032"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr wrap="square" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle>
+            <a:lvl1pPr marL="0" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="de-DE" sz="1100" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t>30°</a:t>
+            </a:r>
+            <a:endParaRPr lang="de-DE" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="12" name="Textfeld 24">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AF90F96A-B2F8-40B7-B114-8B75EF622274}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="21496556" y="7605984"/>
+            <a:ext cx="456935" cy="301777"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr wrap="square" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle>
+            <a:lvl1pPr marL="0" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="de-DE" sz="1100" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t>35°</a:t>
+            </a:r>
+            <a:endParaRPr lang="de-DE" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="13" name="Textfeld 24">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D677C79-4818-4CF1-9F2E-27329B5157B2}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="20613503" y="4006488"/>
+            <a:ext cx="456935" cy="301778"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr wrap="square" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle>
+            <a:lvl1pPr marL="0" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="de-DE" sz="1100" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t>25°</a:t>
+            </a:r>
+            <a:endParaRPr lang="de-DE" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="14" name="Textfeld 24">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E9D19E3-52DA-46E8-8927-E73246454FD6}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="20507995" y="2619342"/>
+            <a:ext cx="456935" cy="301779"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr wrap="square" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle>
+            <a:lvl1pPr marL="0" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="de-DE" sz="1100" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t>20°</a:t>
+            </a:r>
+            <a:endParaRPr lang="de-DE" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="15" name="Textfeld 24">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E94E68E2-3445-4852-AD80-62C5D02A0843}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="20484549" y="1461816"/>
+            <a:ext cx="456935" cy="301779"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr wrap="square" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle>
+            <a:lvl1pPr marL="0" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="de-DE" sz="1100" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t>15°</a:t>
+            </a:r>
+            <a:endParaRPr lang="de-DE" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="16" name="Textfeld 24">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0EE538D8-6793-4350-A1CD-E864D2A177D6}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="20490411" y="748747"/>
+            <a:ext cx="456935" cy="301268"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr wrap="square" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle>
+            <a:lvl1pPr marL="0" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="de-DE" sz="1100" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t>10°</a:t>
+            </a:r>
+            <a:endParaRPr lang="de-DE" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="17" name="Textfeld 24">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8DF3F2C6-83CF-4EB1-AFC6-C32695032CE7}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="20490411" y="351183"/>
+            <a:ext cx="456935" cy="301268"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr wrap="square" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle>
+            <a:lvl1pPr marL="0" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="de-DE" sz="1100" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t>5°</a:t>
+            </a:r>
+            <a:endParaRPr lang="de-DE" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="19" name="Textfeld 24">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{306BB4A8-4B73-20DA-B412-7D315F065AE3}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="18057003" y="6649717"/>
+            <a:ext cx="1713354" cy="301777"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr wrap="square" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle>
+            <a:lvl1pPr marL="0" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="de-DE" sz="1100" i="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t>senkrechter Stoß </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="el-GR" sz="1100" i="1" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Latin Modern Math" panose="02000503000000000000" pitchFamily="50" charset="0"/>
+                <a:ea typeface="Latin Modern Math" panose="02000503000000000000" pitchFamily="50" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t>ϑ</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="de-DE" sz="1100" i="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t> = 0°</a:t>
+            </a:r>
+            <a:endParaRPr lang="de-DE" sz="1100" i="0" baseline="-25000">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="20" name="Freihandform: Form 19">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D00E9615-25F1-8C4F-5C9B-1B7CCB2BCF96}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="19716978" y="6527261"/>
+            <a:ext cx="321013" cy="260391"/>
+          </a:xfrm>
+          <a:custGeom>
+            <a:avLst/>
+            <a:gdLst>
+              <a:gd name="csX0" fmla="*/ 0 w 321013"/>
+              <a:gd name="csY0" fmla="*/ 259404 h 259404"/>
+              <a:gd name="csX1" fmla="*/ 175098 w 321013"/>
+              <a:gd name="csY1" fmla="*/ 201038 h 259404"/>
+              <a:gd name="csX2" fmla="*/ 321013 w 321013"/>
+              <a:gd name="csY2" fmla="*/ 0 h 259404"/>
+            </a:gdLst>
+            <a:ahLst/>
+            <a:cxnLst>
+              <a:cxn ang="0">
+                <a:pos x="csX0" y="csY0"/>
+              </a:cxn>
+              <a:cxn ang="0">
+                <a:pos x="csX1" y="csY1"/>
+              </a:cxn>
+              <a:cxn ang="0">
+                <a:pos x="csX2" y="csY2"/>
+              </a:cxn>
+            </a:cxnLst>
+            <a:rect l="l" t="t" r="r" b="b"/>
+            <a:pathLst>
+              <a:path w="321013" h="259404">
+                <a:moveTo>
+                  <a:pt x="0" y="259404"/>
+                </a:moveTo>
+                <a:cubicBezTo>
+                  <a:pt x="60798" y="251838"/>
+                  <a:pt x="121596" y="244272"/>
+                  <a:pt x="175098" y="201038"/>
+                </a:cubicBezTo>
+                <a:cubicBezTo>
+                  <a:pt x="228600" y="157804"/>
+                  <a:pt x="284805" y="64851"/>
+                  <a:pt x="321013" y="0"/>
+                </a:cubicBezTo>
+              </a:path>
+            </a:pathLst>
+          </a:custGeom>
+          <a:noFill/>
+          <a:ln w="12700" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent4">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="de-DE" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -17785,29 +22401,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{741E214E-2E36-4A17-9BE2-2D8A49B6815B}">
   <dimension ref="B2:G34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="15.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="12" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" style="12" customWidth="1"/>
-    <col min="3" max="7" width="15.77734375" style="12" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" style="12" customWidth="1"/>
+    <col min="3" max="7" width="15.88671875" style="12" customWidth="1"/>
     <col min="8" max="8" width="2.6640625" style="12" customWidth="1"/>
     <col min="9" max="16384" width="11.5546875" style="12"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="B3" s="13"/>
+      <c r="B3" s="29"/>
       <c r="C3" s="6" t="s">
         <v>6</v>
       </c>
@@ -18608,141 +23224,141 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B44C0D16-D85C-4FDC-9177-9539C8122763}">
   <dimension ref="B2:AO50"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="15.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
-    <col min="2" max="41" width="8.77734375" style="1" customWidth="1"/>
+    <col min="2" max="41" width="8.88671875" style="1" customWidth="1"/>
     <col min="42" max="42" width="2.6640625" style="1" customWidth="1"/>
     <col min="43" max="16384" width="11.5546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:41" x14ac:dyDescent="0.4">
-      <c r="B2" s="13" t="s">
+    <row r="2" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B2" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="15" t="s">
+      <c r="C2" s="29"/>
+      <c r="D2" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="16"/>
-      <c r="P2" s="16"/>
-      <c r="Q2" s="16"/>
-      <c r="R2" s="16"/>
-      <c r="S2" s="16"/>
-      <c r="T2" s="16"/>
-      <c r="U2" s="16"/>
-      <c r="V2" s="16"/>
-      <c r="W2" s="16"/>
-      <c r="X2" s="16"/>
-      <c r="Y2" s="16"/>
-      <c r="Z2" s="16"/>
-      <c r="AA2" s="16"/>
-      <c r="AB2" s="16"/>
-      <c r="AC2" s="16"/>
-      <c r="AD2" s="16"/>
-      <c r="AE2" s="16"/>
-      <c r="AF2" s="16"/>
-      <c r="AG2" s="16"/>
-      <c r="AH2" s="16"/>
-      <c r="AI2" s="16"/>
-      <c r="AJ2" s="16"/>
-      <c r="AK2" s="16"/>
-      <c r="AL2" s="16"/>
-      <c r="AM2" s="16"/>
-      <c r="AN2" s="16"/>
-      <c r="AO2" s="17"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="32"/>
+      <c r="Q2" s="32"/>
+      <c r="R2" s="32"/>
+      <c r="S2" s="32"/>
+      <c r="T2" s="32"/>
+      <c r="U2" s="32"/>
+      <c r="V2" s="32"/>
+      <c r="W2" s="32"/>
+      <c r="X2" s="32"/>
+      <c r="Y2" s="32"/>
+      <c r="Z2" s="32"/>
+      <c r="AA2" s="32"/>
+      <c r="AB2" s="32"/>
+      <c r="AC2" s="32"/>
+      <c r="AD2" s="32"/>
+      <c r="AE2" s="32"/>
+      <c r="AF2" s="32"/>
+      <c r="AG2" s="32"/>
+      <c r="AH2" s="32"/>
+      <c r="AI2" s="32"/>
+      <c r="AJ2" s="32"/>
+      <c r="AK2" s="32"/>
+      <c r="AL2" s="32"/>
+      <c r="AM2" s="32"/>
+      <c r="AN2" s="32"/>
+      <c r="AO2" s="33"/>
     </row>
-    <row r="3" spans="2:41" x14ac:dyDescent="0.4">
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="14">
+    <row r="3" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="30">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14">
+      <c r="E3" s="30"/>
+      <c r="F3" s="30">
         <v>1.2</v>
       </c>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14">
+      <c r="G3" s="30"/>
+      <c r="H3" s="30">
         <v>1.3</v>
       </c>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14">
+      <c r="I3" s="30"/>
+      <c r="J3" s="30">
         <v>1.4</v>
       </c>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14">
+      <c r="K3" s="30"/>
+      <c r="L3" s="30">
         <v>1.5</v>
       </c>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14">
+      <c r="M3" s="30"/>
+      <c r="N3" s="30">
         <v>1.6</v>
       </c>
-      <c r="O3" s="14"/>
-      <c r="P3" s="14">
+      <c r="O3" s="30"/>
+      <c r="P3" s="30">
         <v>1.7</v>
       </c>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="14">
+      <c r="Q3" s="30"/>
+      <c r="R3" s="30">
         <v>1.8</v>
       </c>
-      <c r="S3" s="14"/>
-      <c r="T3" s="14">
+      <c r="S3" s="30"/>
+      <c r="T3" s="30">
         <v>1.9</v>
       </c>
-      <c r="U3" s="14"/>
-      <c r="V3" s="14">
+      <c r="U3" s="30"/>
+      <c r="V3" s="30">
         <v>2</v>
       </c>
-      <c r="W3" s="14"/>
-      <c r="X3" s="14">
+      <c r="W3" s="30"/>
+      <c r="X3" s="30">
         <v>2.1</v>
       </c>
-      <c r="Y3" s="14"/>
-      <c r="Z3" s="14">
+      <c r="Y3" s="30"/>
+      <c r="Z3" s="30">
         <v>2.2000000000000002</v>
       </c>
-      <c r="AA3" s="14"/>
-      <c r="AB3" s="14">
+      <c r="AA3" s="30"/>
+      <c r="AB3" s="30">
         <v>2.2999999999999998</v>
       </c>
-      <c r="AC3" s="14"/>
-      <c r="AD3" s="14">
+      <c r="AC3" s="30"/>
+      <c r="AD3" s="30">
         <v>2.4</v>
       </c>
-      <c r="AE3" s="14"/>
-      <c r="AF3" s="14">
+      <c r="AE3" s="30"/>
+      <c r="AF3" s="30">
         <v>3</v>
       </c>
-      <c r="AG3" s="14"/>
-      <c r="AH3" s="14">
+      <c r="AG3" s="30"/>
+      <c r="AH3" s="30">
         <v>4</v>
       </c>
-      <c r="AI3" s="14"/>
-      <c r="AJ3" s="14">
+      <c r="AI3" s="30"/>
+      <c r="AJ3" s="30">
         <v>5</v>
       </c>
-      <c r="AK3" s="14"/>
-      <c r="AL3" s="14">
+      <c r="AK3" s="30"/>
+      <c r="AL3" s="30">
         <v>10</v>
       </c>
-      <c r="AM3" s="14"/>
-      <c r="AN3" s="14">
+      <c r="AM3" s="30"/>
+      <c r="AN3" s="30">
         <v>100000</v>
       </c>
-      <c r="AO3" s="14"/>
+      <c r="AO3" s="30"/>
     </row>
-    <row r="4" spans="2:41" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="11" t="s">
         <v>0</v>
       </c>
@@ -18864,7 +23480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:41" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="9">
         <v>0</v>
       </c>
@@ -18910,7 +23526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:41" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="9">
         <v>2</v>
       </c>
@@ -19071,7 +23687,7 @@
         <v>1.6665348434575749</v>
       </c>
     </row>
-    <row r="7" spans="2:41" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="9">
         <v>4</v>
       </c>
@@ -19232,7 +23848,7 @@
         <v>3.3322782952338765</v>
       </c>
     </row>
-    <row r="8" spans="2:41" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="9">
         <v>6</v>
       </c>
@@ -19393,7 +24009,7 @@
         <v>4.9964310819001581</v>
       </c>
     </row>
-    <row r="9" spans="2:41" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="9">
         <v>8</v>
       </c>
@@ -19554,7 +24170,7 @@
         <v>6.6581792172359293</v>
       </c>
     </row>
-    <row r="10" spans="2:41" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="9">
         <v>10</v>
       </c>
@@ -19715,7 +24331,7 @@
         <v>8.3166858207722125</v>
       </c>
     </row>
-    <row r="11" spans="2:41" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="9">
         <v>12</v>
       </c>
@@ -19876,7 +24492,7 @@
         <v>9.971082813261372</v>
       </c>
     </row>
-    <row r="12" spans="2:41" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="9">
         <v>14</v>
       </c>
@@ -20037,7 +24653,7 @@
         <v>11.62046195778616</v>
       </c>
     </row>
-    <row r="13" spans="2:41" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="9">
         <v>16</v>
       </c>
@@ -20198,7 +24814,7 @@
         <v>13.26386506493875</v>
       </c>
     </row>
-    <row r="14" spans="2:41" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="9">
         <v>18</v>
       </c>
@@ -20359,7 +24975,7 @@
         <v>14.900273135674098</v>
       </c>
     </row>
-    <row r="15" spans="2:41" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="9">
         <v>20</v>
       </c>
@@ -20520,7 +25136,7 @@
         <v>16.528594175104608</v>
       </c>
     </row>
-    <row r="16" spans="2:41" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B16" s="9">
         <v>22</v>
       </c>
@@ -20681,7 +25297,7 @@
         <v>18.14764936005497</v>
       </c>
     </row>
-    <row r="17" spans="2:41" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="9">
         <v>24</v>
       </c>
@@ -20842,7 +25458,7 @@
         <v>19.756157178702612</v>
       </c>
     </row>
-    <row r="18" spans="2:41" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="9">
         <v>26</v>
       </c>
@@ -21003,7 +25619,7 @@
         <v>21.352715078064691</v>
       </c>
     </row>
-    <row r="19" spans="2:41" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B19" s="9">
         <v>28</v>
       </c>
@@ -21164,7 +25780,7 @@
         <v>22.935778049257106</v>
       </c>
     </row>
-    <row r="20" spans="2:41" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B20" s="9">
         <v>30</v>
       </c>
@@ -21325,7 +25941,7 @@
         <v>24.503633444419975</v>
       </c>
     </row>
-    <row r="21" spans="2:41" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B21" s="9">
         <v>32</v>
       </c>
@@ -21486,7 +26102,7 @@
         <v>26.054371143665815</v>
       </c>
     </row>
-    <row r="22" spans="2:41" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="9">
         <v>34</v>
       </c>
@@ -21647,7 +26263,7 @@
         <v>27.585847962766874</v>
       </c>
     </row>
-    <row r="23" spans="2:41" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="9">
         <v>36</v>
       </c>
@@ -21808,7 +26424,7 @@
         <v>29.095644895408221</v>
       </c>
     </row>
-    <row r="24" spans="2:41" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="9">
         <v>38</v>
       </c>
@@ -21969,7 +26585,7 @@
         <v>30.581015394182749</v>
       </c>
     </row>
-    <row r="25" spans="2:41" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="9">
         <v>40</v>
       </c>
@@ -22130,7 +26746,7 @@
         <v>32.038822379635519</v>
       </c>
     </row>
-    <row r="26" spans="2:41" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="9">
         <v>42</v>
       </c>
@@ -22291,7 +26907,7 @@
         <v>33.465460981431455</v>
       </c>
     </row>
-    <row r="27" spans="2:41" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="9">
         <v>44</v>
       </c>
@@ -22452,7 +27068,7 @@
         <v>34.856763096865599</v>
       </c>
     </row>
-    <row r="28" spans="2:41" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="9">
         <v>46</v>
       </c>
@@ -22613,7 +27229,7 @@
         <v>36.207878610169722</v>
       </c>
     </row>
-    <row r="29" spans="2:41" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B29" s="9">
         <v>48</v>
       </c>
@@ -22774,7 +27390,7 @@
         <v>37.513126424466854</v>
       </c>
     </row>
-    <row r="30" spans="2:41" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B30" s="9">
         <v>50</v>
       </c>
@@ -22935,7 +27551,7 @@
         <v>38.765806135175815</v>
       </c>
     </row>
-    <row r="31" spans="2:41" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B31" s="9">
         <v>52</v>
       </c>
@@ -23096,7 +27712,7 @@
         <v>39.95795795787128</v>
       </c>
     </row>
-    <row r="32" spans="2:41" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="9">
         <v>54</v>
       </c>
@@ -23257,7 +27873,7 @@
         <v>41.080054037650292</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="9">
         <v>56</v>
       </c>
@@ -23418,7 +28034,7 @@
         <v>42.12059796518809</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B34" s="9">
         <v>58</v>
       </c>
@@ -23579,7 +28195,7 @@
         <v>43.0656004204331</v>
       </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B35" s="9">
         <v>60</v>
       </c>
@@ -23740,7 +28356,7 @@
         <v>43.897886237835607</v>
       </c>
     </row>
-    <row r="36" spans="2:41" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B36" s="9">
         <v>62</v>
       </c>
@@ -23901,7 +28517,7 @@
         <v>44.596170282060555</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B37" s="9">
         <v>64</v>
       </c>
@@ -24062,7 +28678,7 @@
         <v>45.133814301010069</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="9">
         <v>66</v>
       </c>
@@ -24223,7 +28839,7 @@
         <v>45.477142046063676</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="9">
         <v>68</v>
       </c>
@@ -24384,7 +29000,7 @@
         <v>45.583143727667405</v>
       </c>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.4">
+    <row r="40" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="9">
         <v>70</v>
       </c>
@@ -24545,7 +29161,7 @@
         <v>45.396345385689813</v>
       </c>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B41" s="9">
         <v>72</v>
       </c>
@@ -24706,7 +29322,7 @@
         <v>44.844568824817372</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.4">
+    <row r="42" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B42" s="9">
         <v>74</v>
       </c>
@@ -24867,7 +29483,7 @@
         <v>43.833315061383509</v>
       </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.4">
+    <row r="43" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B43" s="9">
         <v>76</v>
       </c>
@@ -25028,7 +29644,7 @@
         <v>42.238718248161092</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.4">
+    <row r="44" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B44" s="9">
         <v>78</v>
       </c>
@@ -25189,7 +29805,7 @@
         <v>39.899827541505466</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.4">
+    <row r="45" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B45" s="9">
         <v>80</v>
       </c>
@@ -25350,7 +29966,7 @@
         <v>36.613292079058084</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.4">
+    <row r="46" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B46" s="9">
         <v>82</v>
       </c>
@@ -25511,7 +30127,7 @@
         <v>32.13909391350419</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B47" s="9">
         <v>84</v>
       </c>
@@ -25672,7 +30288,7 @@
         <v>26.236572594335257</v>
       </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B48" s="9">
         <v>86</v>
       </c>
@@ -25833,7 +30449,7 @@
         <v>18.761014913932325</v>
       </c>
     </row>
-    <row r="49" spans="2:41" x14ac:dyDescent="0.4">
+    <row r="49" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B49" s="9">
         <v>88</v>
       </c>
@@ -25994,7 +30610,7 @@
         <v>9.8336896170272219</v>
       </c>
     </row>
-    <row r="50" spans="2:41" x14ac:dyDescent="0.4">
+    <row r="50" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B50" s="9">
         <v>90</v>
       </c>
@@ -26157,11 +30773,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="B2:C3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
     <mergeCell ref="AJ3:AK3"/>
     <mergeCell ref="AL3:AM3"/>
     <mergeCell ref="AN3:AO3"/>
@@ -26178,6 +30789,11 @@
     <mergeCell ref="V3:W3"/>
     <mergeCell ref="X3:Y3"/>
     <mergeCell ref="D3:E3"/>
+    <mergeCell ref="B2:C3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -26190,34 +30806,34 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BF15A72-F308-4BD9-B417-7604850B60FE}">
   <dimension ref="B2:K62"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="15.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
-    <col min="2" max="3" width="8.77734375" style="1" customWidth="1"/>
-    <col min="4" max="11" width="13.77734375" style="1" customWidth="1"/>
+    <col min="2" max="3" width="8.88671875" style="1" customWidth="1"/>
+    <col min="4" max="11" width="13.88671875" style="1" customWidth="1"/>
     <col min="12" max="12" width="2.6640625" style="1" customWidth="1"/>
     <col min="13" max="16384" width="11.5546875" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="19"/>
-      <c r="D2" s="13" t="s">
+      <c r="C2" s="35"/>
+      <c r="D2" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B3" s="20"/>
-      <c r="C3" s="21"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="37"/>
       <c r="D3" s="7">
         <v>0</v>
       </c>
@@ -28134,4 +32750,2215 @@
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4FED479-4888-4085-B5E0-2E4B7F918E18}">
+  <dimension ref="B2:AC74"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="15.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" style="19" customWidth="1"/>
+    <col min="3" max="3" width="13.88671875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" style="24" customWidth="1"/>
+    <col min="5" max="5" width="13.88671875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.88671875" style="24" customWidth="1"/>
+    <col min="7" max="7" width="13.88671875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.88671875" style="24" customWidth="1"/>
+    <col min="9" max="9" width="13.88671875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="13.88671875" style="24" customWidth="1"/>
+    <col min="11" max="11" width="13.88671875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="13.88671875" style="24" customWidth="1"/>
+    <col min="13" max="13" width="13.88671875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="13.88671875" style="24" customWidth="1"/>
+    <col min="15" max="15" width="13.88671875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="13.88671875" style="24" customWidth="1"/>
+    <col min="17" max="17" width="13.88671875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="2.6640625" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="11.5546875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:29" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B2" s="43" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="N2" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="P2" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q2" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="2:29" x14ac:dyDescent="0.4">
+      <c r="B3" s="44"/>
+      <c r="C3" s="7">
+        <v>0</v>
+      </c>
+      <c r="D3" s="41"/>
+      <c r="E3" s="38">
+        <v>5</v>
+      </c>
+      <c r="F3" s="41"/>
+      <c r="G3" s="38">
+        <v>10</v>
+      </c>
+      <c r="H3" s="41"/>
+      <c r="I3" s="38">
+        <v>15</v>
+      </c>
+      <c r="J3" s="41"/>
+      <c r="K3" s="38">
+        <v>20</v>
+      </c>
+      <c r="L3" s="41"/>
+      <c r="M3" s="38">
+        <v>25</v>
+      </c>
+      <c r="N3" s="41"/>
+      <c r="O3" s="38">
+        <v>30</v>
+      </c>
+      <c r="P3" s="41"/>
+      <c r="Q3" s="38">
+        <v>35</v>
+      </c>
+      <c r="AC3"/>
+    </row>
+    <row r="4" spans="2:29" x14ac:dyDescent="0.4">
+      <c r="B4" s="44"/>
+      <c r="C4" s="8">
+        <f>C3*PI()/180</f>
+        <v>0</v>
+      </c>
+      <c r="D4" s="41"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="39"/>
+      <c r="L4" s="41"/>
+      <c r="M4" s="39"/>
+      <c r="N4" s="41"/>
+      <c r="O4" s="39"/>
+      <c r="P4" s="41"/>
+      <c r="Q4" s="39"/>
+    </row>
+    <row r="5" spans="2:29" x14ac:dyDescent="0.4">
+      <c r="B5" s="45"/>
+      <c r="C5" s="14">
+        <f>PI()/2</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="D5" s="42"/>
+      <c r="E5" s="15">
+        <v>1.5</v>
+      </c>
+      <c r="F5" s="42"/>
+      <c r="G5" s="15">
+        <v>1.46</v>
+      </c>
+      <c r="H5" s="42"/>
+      <c r="I5" s="15">
+        <v>1.42</v>
+      </c>
+      <c r="J5" s="42"/>
+      <c r="K5" s="23">
+        <v>1.39</v>
+      </c>
+      <c r="L5" s="42"/>
+      <c r="M5" s="23">
+        <v>1.36</v>
+      </c>
+      <c r="N5" s="42"/>
+      <c r="O5" s="23">
+        <v>1.32</v>
+      </c>
+      <c r="P5" s="42"/>
+      <c r="Q5" s="23">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="6" spans="2:29" x14ac:dyDescent="0.4">
+      <c r="B6" s="21">
+        <v>1</v>
+      </c>
+      <c r="C6" s="18">
+        <f>((((1.4+1)/2)^(1.4+1)*($B6*SIN(C$5))^(2*1.4))/((1+((1.4-1)/2)*($B6*SIN(C$5))^2)^1.4*(1.4*($B6*SIN(C$5))^2-((1.4-1)/2))))^((1)/(1.4-1))</f>
+        <v>1</v>
+      </c>
+      <c r="D6" s="10"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="10"/>
+      <c r="Q6" s="5"/>
+    </row>
+    <row r="7" spans="2:29" x14ac:dyDescent="0.4">
+      <c r="B7" s="20">
+        <v>1.05</v>
+      </c>
+      <c r="C7" s="5">
+        <f t="shared" ref="C7:C56" si="0">((((1.4+1)/2)^(1.4+1)*($B7*SIN(C$5))^(2*1.4))/((1+((1.4-1)/2)*($B7*SIN(C$5))^2)^1.4*(1.4*($B7*SIN(C$5))^2-((1.4-1)/2))))^((1)/(1.4-1))</f>
+        <v>0.99985299009517314</v>
+      </c>
+      <c r="D7" s="10"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="10"/>
+      <c r="Q7" s="5"/>
+    </row>
+    <row r="8" spans="2:29" x14ac:dyDescent="0.4">
+      <c r="B8" s="20">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C8" s="5">
+        <f t="shared" si="0"/>
+        <v>0.99892801531447117</v>
+      </c>
+      <c r="D8" s="10">
+        <v>3.5</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0.99199999999999999</v>
+      </c>
+      <c r="F8" s="10">
+        <v>3.5</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0.94699999999999995</v>
+      </c>
+      <c r="H8" s="10"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="5"/>
+    </row>
+    <row r="9" spans="2:29" x14ac:dyDescent="0.4">
+      <c r="B9" s="20">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="C9" s="5">
+        <f t="shared" si="0"/>
+        <v>0.99668975878988608</v>
+      </c>
+      <c r="D9" s="10">
+        <v>3.5</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0.99199999999999999</v>
+      </c>
+      <c r="F9" s="10">
+        <v>3</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0.96299999999999997</v>
+      </c>
+      <c r="H9" s="10">
+        <v>3.5</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0.85299999999999998</v>
+      </c>
+      <c r="J9" s="10"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="10"/>
+      <c r="Q9" s="5"/>
+    </row>
+    <row r="10" spans="2:29" x14ac:dyDescent="0.4">
+      <c r="B10" s="20">
+        <v>1.2</v>
+      </c>
+      <c r="C10" s="5">
+        <f t="shared" si="0"/>
+        <v>0.99279839769936207</v>
+      </c>
+      <c r="D10" s="10">
+        <v>3</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0.99480000000000002</v>
+      </c>
+      <c r="F10" s="10">
+        <v>2.5</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0.97599999999999998</v>
+      </c>
+      <c r="H10" s="10">
+        <v>3</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0.89549999999999996</v>
+      </c>
+      <c r="J10" s="10"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="5"/>
+    </row>
+    <row r="11" spans="2:29" x14ac:dyDescent="0.4">
+      <c r="B11" s="20">
+        <v>1.25</v>
+      </c>
+      <c r="C11" s="5">
+        <f t="shared" si="0"/>
+        <v>0.98705677037193806</v>
+      </c>
+      <c r="D11" s="10">
+        <v>2.5</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0.997</v>
+      </c>
+      <c r="F11" s="10">
+        <v>2</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0.98509999999999998</v>
+      </c>
+      <c r="H11" s="10">
+        <v>2.5</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0.92900000000000005</v>
+      </c>
+      <c r="J11" s="10">
+        <v>3.5</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0.72799999999999998</v>
+      </c>
+      <c r="L11" s="10"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="10"/>
+      <c r="Q11" s="5"/>
+    </row>
+    <row r="12" spans="2:29" x14ac:dyDescent="0.4">
+      <c r="B12" s="20">
+        <v>1.3</v>
+      </c>
+      <c r="C12" s="5">
+        <f t="shared" si="0"/>
+        <v>0.97937364894321854</v>
+      </c>
+      <c r="D12" s="10">
+        <v>2</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0.99860000000000004</v>
+      </c>
+      <c r="F12" s="10">
+        <v>1.8</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0.98719999999999997</v>
+      </c>
+      <c r="H12" s="10">
+        <v>2.25</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0.9425</v>
+      </c>
+      <c r="J12" s="10">
+        <v>3</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0.79700000000000004</v>
+      </c>
+      <c r="L12" s="10"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="10"/>
+      <c r="Q12" s="5"/>
+      <c r="AB12"/>
+      <c r="AC12"/>
+    </row>
+    <row r="13" spans="2:29" x14ac:dyDescent="0.4">
+      <c r="B13" s="20">
+        <v>1.35</v>
+      </c>
+      <c r="C13" s="5">
+        <f t="shared" si="0"/>
+        <v>0.96973709318744861</v>
+      </c>
+      <c r="D13" s="10">
+        <v>1.8</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0.999</v>
+      </c>
+      <c r="F13" s="10">
+        <v>1.6</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0.98839999999999995</v>
+      </c>
+      <c r="H13" s="10">
+        <v>2</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0.95299999999999996</v>
+      </c>
+      <c r="J13" s="10">
+        <v>2.5</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0.85499999999999998</v>
+      </c>
+      <c r="L13" s="10">
+        <v>3.5</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0.59150000000000003</v>
+      </c>
+      <c r="N13" s="10"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="10"/>
+      <c r="Q13" s="5"/>
+    </row>
+    <row r="14" spans="2:29" x14ac:dyDescent="0.4">
+      <c r="B14" s="20">
+        <v>1.4</v>
+      </c>
+      <c r="C14" s="5">
+        <f t="shared" si="0"/>
+        <v>0.95819441491554602</v>
+      </c>
+      <c r="D14" s="10">
+        <v>1.6</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0.99909999999999999</v>
+      </c>
+      <c r="F14" s="10">
+        <v>1.47</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0.98670000000000002</v>
+      </c>
+      <c r="H14" s="10">
+        <v>1.8</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0.95730000000000004</v>
+      </c>
+      <c r="J14" s="10">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0.874</v>
+      </c>
+      <c r="L14" s="10">
+        <v>3.1</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0.66149999999999998</v>
+      </c>
+      <c r="N14" s="10"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="5"/>
+    </row>
+    <row r="15" spans="2:29" x14ac:dyDescent="0.4">
+      <c r="B15" s="20">
+        <v>1.45</v>
+      </c>
+      <c r="C15" s="5">
+        <f t="shared" si="0"/>
+        <v>0.94483668541179422</v>
+      </c>
+      <c r="D15" s="10">
+        <v>1.3</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0.99860000000000004</v>
+      </c>
+      <c r="F15" s="26">
+        <v>1.42</v>
+      </c>
+      <c r="G15" s="18">
+        <v>0.97499999999999998</v>
+      </c>
+      <c r="H15" s="10">
+        <v>1.68</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0.95499999999999996</v>
+      </c>
+      <c r="J15" s="10">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0.88200000000000001</v>
+      </c>
+      <c r="L15" s="10">
+        <v>2.8</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0.71199999999999997</v>
+      </c>
+      <c r="N15" s="10"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="10"/>
+      <c r="Q15" s="5"/>
+    </row>
+    <row r="16" spans="2:29" x14ac:dyDescent="0.4">
+      <c r="B16" s="20">
+        <v>1.5</v>
+      </c>
+      <c r="C16" s="5">
+        <f t="shared" si="0"/>
+        <v>0.92978651228282927</v>
+      </c>
+      <c r="D16" s="26">
+        <v>1.24</v>
+      </c>
+      <c r="E16" s="18">
+        <v>0.99529999999999996</v>
+      </c>
+      <c r="F16" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0.94299999999999995</v>
+      </c>
+      <c r="H16" s="26">
+        <v>1.615</v>
+      </c>
+      <c r="I16" s="18">
+        <v>0.94</v>
+      </c>
+      <c r="J16" s="10">
+        <v>2.1</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0.88900000000000001</v>
+      </c>
+      <c r="L16" s="10">
+        <v>2.5</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0.75649999999999995</v>
+      </c>
+      <c r="N16" s="10"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="10"/>
+      <c r="Q16" s="5"/>
+    </row>
+    <row r="17" spans="2:28" x14ac:dyDescent="0.4">
+      <c r="B17" s="20">
+        <v>1.55</v>
+      </c>
+      <c r="C17" s="5">
+        <f t="shared" si="0"/>
+        <v>0.91318827243034917</v>
+      </c>
+      <c r="D17" s="10">
+        <v>1.3</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0.98199999999999998</v>
+      </c>
+      <c r="F17" s="10">
+        <v>1.6</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0.90639999999999998</v>
+      </c>
+      <c r="H17" s="10">
+        <v>1.65</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0.90900000000000003</v>
+      </c>
+      <c r="J17" s="10">
+        <v>2</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0.89280000000000004</v>
+      </c>
+      <c r="L17" s="10">
+        <v>2.4</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0.76880000000000004</v>
+      </c>
+      <c r="N17" s="10"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="10"/>
+      <c r="Q17" s="5"/>
+    </row>
+    <row r="18" spans="2:28" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B18" s="20">
+        <v>1.6</v>
+      </c>
+      <c r="C18" s="5">
+        <f t="shared" si="0"/>
+        <v>0.89520026046533652</v>
+      </c>
+      <c r="D18" s="27">
+        <v>1.4</v>
+      </c>
+      <c r="E18" s="17">
+        <v>0.96099999999999997</v>
+      </c>
+      <c r="F18" s="10">
+        <v>1.7</v>
+      </c>
+      <c r="G18" s="5">
+        <v>0.86599999999999999</v>
+      </c>
+      <c r="H18" s="10">
+        <v>1.7</v>
+      </c>
+      <c r="I18" s="5">
+        <v>0.88300000000000001</v>
+      </c>
+      <c r="J18" s="10">
+        <v>1.875</v>
+      </c>
+      <c r="K18" s="5">
+        <v>0.89</v>
+      </c>
+      <c r="L18" s="10">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="M18" s="5">
+        <v>0.77900000000000003</v>
+      </c>
+      <c r="N18" s="10"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="10"/>
+      <c r="Q18" s="5"/>
+    </row>
+    <row r="19" spans="2:28" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B19" s="20">
+        <v>1.65</v>
+      </c>
+      <c r="C19" s="5">
+        <f t="shared" si="0"/>
+        <v>0.87598837652705697</v>
+      </c>
+      <c r="D19" s="25">
+        <v>1.5</v>
+      </c>
+      <c r="E19" s="16">
+        <f>((((1.4+1)/2)^(1.4+1)*($D19*SIN(E$5))^(2*1.4))/((1+((1.4-1)/2)*($D19*SIN(E$5))^2)^1.4*(1.4*($D19*SIN(E$5))^2-((1.4-1)/2))))^((1)/(1.4-1))</f>
+        <v>0.93097323536631904</v>
+      </c>
+      <c r="F19" s="27">
+        <v>1.8</v>
+      </c>
+      <c r="G19" s="17">
+        <v>0.82199999999999995</v>
+      </c>
+      <c r="H19" s="10">
+        <v>1.8</v>
+      </c>
+      <c r="I19" s="5">
+        <v>0.83499999999999996</v>
+      </c>
+      <c r="J19" s="26">
+        <v>1.8380000000000001</v>
+      </c>
+      <c r="K19" s="18">
+        <v>0.86899999999999999</v>
+      </c>
+      <c r="L19" s="10">
+        <v>2.21</v>
+      </c>
+      <c r="M19" s="5">
+        <v>0.78300000000000003</v>
+      </c>
+      <c r="N19" s="10">
+        <v>3.5</v>
+      </c>
+      <c r="O19" s="5">
+        <v>0.46500000000000002</v>
+      </c>
+      <c r="P19" s="10"/>
+      <c r="Q19" s="5"/>
+    </row>
+    <row r="20" spans="2:28" x14ac:dyDescent="0.4">
+      <c r="B20" s="20">
+        <v>1.7</v>
+      </c>
+      <c r="C20" s="5">
+        <f t="shared" si="0"/>
+        <v>0.85572107902379757</v>
+      </c>
+      <c r="D20" s="10">
+        <v>1.6</v>
+      </c>
+      <c r="E20" s="5">
+        <f t="shared" ref="E20:E39" si="1">((((1.4+1)/2)^(1.4+1)*($D20*SIN(E$5))^(2*1.4))/((1+((1.4-1)/2)*($D20*SIN(E$5))^2)^1.4*(1.4*($D20*SIN(E$5))^2-((1.4-1)/2))))^((1)/(1.4-1))</f>
+        <v>0.89668953855954769</v>
+      </c>
+      <c r="F20" s="25">
+        <v>1.9</v>
+      </c>
+      <c r="G20" s="16">
+        <f t="shared" ref="G20:I36" si="2">((((1.4+1)/2)^(1.4+1)*(F20*SIN(G$5))^(2*1.4))/((1+((1.4-1)/2)*(F20*SIN(G$5))^2)^1.4*(1.4*(F20*SIN(G$5))^2-((1.4-1)/2))))^((1)/(1.4-1))</f>
+        <v>0.77271704449629175</v>
+      </c>
+      <c r="H20" s="10">
+        <v>1.9</v>
+      </c>
+      <c r="I20" s="16">
+        <v>0.78600000000000003</v>
+      </c>
+      <c r="J20" s="10">
+        <v>1.9</v>
+      </c>
+      <c r="K20" s="5">
+        <v>0.81299999999999994</v>
+      </c>
+      <c r="L20" s="10">
+        <v>2.15</v>
+      </c>
+      <c r="M20" s="5">
+        <v>0.77800000000000002</v>
+      </c>
+      <c r="N20" s="10">
+        <v>3.3</v>
+      </c>
+      <c r="O20" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="P20" s="10"/>
+      <c r="Q20" s="5"/>
+    </row>
+    <row r="21" spans="2:28" x14ac:dyDescent="0.4">
+      <c r="B21" s="20">
+        <v>1.75</v>
+      </c>
+      <c r="C21" s="5">
+        <f t="shared" si="0"/>
+        <v>0.83456539208449942</v>
+      </c>
+      <c r="D21" s="10">
+        <v>1.7</v>
+      </c>
+      <c r="E21" s="5">
+        <f t="shared" si="1"/>
+        <v>0.85748419479104809</v>
+      </c>
+      <c r="F21" s="10">
+        <v>2</v>
+      </c>
+      <c r="G21" s="16">
+        <f t="shared" si="2"/>
+        <v>0.72660209482121385</v>
+      </c>
+      <c r="H21" s="10">
+        <v>2</v>
+      </c>
+      <c r="I21" s="16">
+        <v>0.73699999999999999</v>
+      </c>
+      <c r="J21" s="10">
+        <v>2</v>
+      </c>
+      <c r="K21" s="5">
+        <v>0.75600000000000001</v>
+      </c>
+      <c r="L21" s="26">
+        <v>2.1259999999999999</v>
+      </c>
+      <c r="M21" s="18">
+        <v>0.75900000000000001</v>
+      </c>
+      <c r="N21" s="25">
+        <v>3.1</v>
+      </c>
+      <c r="O21" s="5">
+        <v>0.53700000000000003</v>
+      </c>
+      <c r="P21" s="25"/>
+      <c r="Q21" s="5"/>
+    </row>
+    <row r="22" spans="2:28" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B22" s="20">
+        <v>1.8</v>
+      </c>
+      <c r="C22" s="5">
+        <f t="shared" si="0"/>
+        <v>0.81268379959868853</v>
+      </c>
+      <c r="D22" s="10">
+        <v>1.8</v>
+      </c>
+      <c r="E22" s="5">
+        <f t="shared" si="1"/>
+        <v>0.81468275132784285</v>
+      </c>
+      <c r="F22" s="10">
+        <v>2.1</v>
+      </c>
+      <c r="G22" s="16">
+        <f t="shared" si="2"/>
+        <v>0.68019385655875653</v>
+      </c>
+      <c r="H22" s="27">
+        <v>2.1</v>
+      </c>
+      <c r="I22" s="17">
+        <v>0.68899999999999995</v>
+      </c>
+      <c r="J22" s="10">
+        <v>2.1</v>
+      </c>
+      <c r="K22" s="5">
+        <v>0.70199999999999996</v>
+      </c>
+      <c r="L22" s="10">
+        <v>2.15</v>
+      </c>
+      <c r="M22" s="5">
+        <v>0.72199999999999998</v>
+      </c>
+      <c r="N22" s="10">
+        <v>2.9</v>
+      </c>
+      <c r="O22" s="5">
+        <v>0.57250000000000001</v>
+      </c>
+      <c r="P22" s="10"/>
+      <c r="Q22" s="5"/>
+    </row>
+    <row r="23" spans="2:28" x14ac:dyDescent="0.4">
+      <c r="B23" s="20">
+        <v>1.85</v>
+      </c>
+      <c r="C23" s="5">
+        <f t="shared" si="0"/>
+        <v>0.79023188655348287</v>
+      </c>
+      <c r="D23" s="10">
+        <v>1.9</v>
+      </c>
+      <c r="E23" s="5">
+        <f t="shared" si="1"/>
+        <v>0.76954852360491333</v>
+      </c>
+      <c r="F23" s="10">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="G23" s="16">
+        <f t="shared" si="2"/>
+        <v>0.63429111067139099</v>
+      </c>
+      <c r="H23" s="25">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="I23" s="16">
+        <f t="shared" si="2"/>
+        <v>0.63954414111559987</v>
+      </c>
+      <c r="J23" s="25">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="K23" s="16">
+        <v>0.65100000000000002</v>
+      </c>
+      <c r="L23" s="25">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="M23" s="5">
+        <v>0.68600000000000005</v>
+      </c>
+      <c r="N23" s="10">
+        <v>2.7</v>
+      </c>
+      <c r="O23" s="5">
+        <v>0.60299999999999998</v>
+      </c>
+      <c r="P23" s="10"/>
+      <c r="Q23" s="5"/>
+      <c r="AB23"/>
+    </row>
+    <row r="24" spans="2:28" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B24" s="20">
+        <v>1.9</v>
+      </c>
+      <c r="C24" s="5">
+        <f t="shared" si="0"/>
+        <v>0.76735660925323457</v>
+      </c>
+      <c r="D24" s="10">
+        <v>2</v>
+      </c>
+      <c r="E24" s="5">
+        <f t="shared" si="1"/>
+        <v>0.72321447596145572</v>
+      </c>
+      <c r="F24" s="10">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G24" s="16">
+        <f t="shared" si="2"/>
+        <v>0.5895251960035558</v>
+      </c>
+      <c r="H24" s="10">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="I24" s="16">
+        <f t="shared" si="2"/>
+        <v>0.59485187765508241</v>
+      </c>
+      <c r="J24" s="27">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="K24" s="17">
+        <v>0.60299999999999998</v>
+      </c>
+      <c r="L24" s="10">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="M24" s="5">
+        <v>0.627</v>
+      </c>
+      <c r="N24" s="10">
+        <v>2.5649999999999999</v>
+      </c>
+      <c r="O24" s="5">
+        <v>0.61199999999999999</v>
+      </c>
+      <c r="P24" s="10"/>
+      <c r="Q24" s="5"/>
+    </row>
+    <row r="25" spans="2:28" x14ac:dyDescent="0.4">
+      <c r="B25" s="20">
+        <v>1.95</v>
+      </c>
+      <c r="C25" s="5">
+        <f t="shared" si="0"/>
+        <v>0.74419509207184276</v>
+      </c>
+      <c r="D25" s="10">
+        <v>2.1</v>
+      </c>
+      <c r="E25" s="5">
+        <f t="shared" si="1"/>
+        <v>0.67664948152984683</v>
+      </c>
+      <c r="F25" s="10">
+        <v>2.4</v>
+      </c>
+      <c r="G25" s="16">
+        <f t="shared" si="2"/>
+        <v>0.54637360468298235</v>
+      </c>
+      <c r="H25" s="10">
+        <v>2.4</v>
+      </c>
+      <c r="I25" s="16">
+        <f t="shared" si="2"/>
+        <v>0.55170761073228358</v>
+      </c>
+      <c r="J25" s="25">
+        <v>2.4</v>
+      </c>
+      <c r="K25" s="16">
+        <f t="shared" ref="K25" si="3">((((1.4+1)/2)^(1.4+1)*(H25*SIN(K$5))^(2*1.4))/((1+((1.4-1)/2)*(H25*SIN(K$5))^2)^1.4*(1.4*(H25*SIN(K$5))^2-((1.4-1)/2))))^((1)/(1.4-1))</f>
+        <v>0.55679831860296347</v>
+      </c>
+      <c r="L25" s="10">
+        <v>2.4</v>
+      </c>
+      <c r="M25" s="5">
+        <v>0.57599999999999996</v>
+      </c>
+      <c r="N25" s="26">
+        <v>2.516</v>
+      </c>
+      <c r="O25" s="18">
+        <v>0.59350000000000003</v>
+      </c>
+      <c r="P25" s="10"/>
+      <c r="Q25" s="5"/>
+    </row>
+    <row r="26" spans="2:28" x14ac:dyDescent="0.4">
+      <c r="B26" s="20">
+        <v>2</v>
+      </c>
+      <c r="C26" s="5">
+        <f t="shared" si="0"/>
+        <v>0.72087386148474575</v>
+      </c>
+      <c r="D26" s="10">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="E26" s="5">
+        <f t="shared" si="1"/>
+        <v>0.63064814286359361</v>
+      </c>
+      <c r="F26" s="10">
+        <v>2.5</v>
+      </c>
+      <c r="G26" s="16">
+        <f t="shared" si="2"/>
+        <v>0.50517853734810947</v>
+      </c>
+      <c r="H26" s="10">
+        <v>2.5</v>
+      </c>
+      <c r="I26" s="16">
+        <f t="shared" si="2"/>
+        <v>0.51046350829404075</v>
+      </c>
+      <c r="J26" s="10">
+        <v>2.5</v>
+      </c>
+      <c r="K26" s="16">
+        <f t="shared" ref="K26:K28" si="4">((((1.4+1)/2)^(1.4+1)*(H26*SIN(K$5))^(2*1.4))/((1+((1.4-1)/2)*(H26*SIN(K$5))^2)^1.4*(1.4*(H26*SIN(K$5))^2-((1.4-1)/2))))^((1)/(1.4-1))</f>
+        <v>0.51551387521716441</v>
+      </c>
+      <c r="L26" s="10">
+        <v>2.5</v>
+      </c>
+      <c r="M26" s="5">
+        <v>0.52900000000000003</v>
+      </c>
+      <c r="N26" s="10">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="O26" s="5">
+        <v>0.55400000000000005</v>
+      </c>
+      <c r="P26" s="10"/>
+      <c r="Q26" s="5"/>
+    </row>
+    <row r="27" spans="2:28" x14ac:dyDescent="0.4">
+      <c r="B27" s="20">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="C27" s="5">
+        <f t="shared" si="0"/>
+        <v>0.69750843932096973</v>
+      </c>
+      <c r="D27" s="10">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="E27" s="5">
+        <f t="shared" si="1"/>
+        <v>0.58583596022247098</v>
+      </c>
+      <c r="F27" s="10">
+        <v>2.6</v>
+      </c>
+      <c r="G27" s="16">
+        <f t="shared" si="2"/>
+        <v>0.46616732721433957</v>
+      </c>
+      <c r="H27" s="10">
+        <v>2.6</v>
+      </c>
+      <c r="I27" s="16">
+        <f t="shared" si="2"/>
+        <v>0.471356720670987</v>
+      </c>
+      <c r="J27" s="10">
+        <v>2.6</v>
+      </c>
+      <c r="K27" s="16">
+        <f t="shared" si="4"/>
+        <v>0.47632163636926</v>
+      </c>
+      <c r="L27" s="10">
+        <v>2.6</v>
+      </c>
+      <c r="M27" s="5">
+        <v>0.48599999999999999</v>
+      </c>
+      <c r="N27" s="25">
+        <v>2.6</v>
+      </c>
+      <c r="O27" s="16">
+        <v>0.52200000000000002</v>
+      </c>
+      <c r="P27" s="25"/>
+      <c r="Q27" s="5"/>
+    </row>
+    <row r="28" spans="2:28" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B28" s="20">
+        <v>2.1</v>
+      </c>
+      <c r="C28" s="5">
+        <f t="shared" si="0"/>
+        <v>0.67420322706305214</v>
+      </c>
+      <c r="D28" s="10">
+        <v>2.4</v>
+      </c>
+      <c r="E28" s="5">
+        <f t="shared" si="1"/>
+        <v>0.54268371015872352</v>
+      </c>
+      <c r="F28" s="10">
+        <v>2.7</v>
+      </c>
+      <c r="G28" s="16">
+        <f t="shared" si="2"/>
+        <v>0.4294726999735734</v>
+      </c>
+      <c r="H28" s="10">
+        <v>2.7</v>
+      </c>
+      <c r="I28" s="16">
+        <f t="shared" si="2"/>
+        <v>0.43452921921018928</v>
+      </c>
+      <c r="J28" s="10">
+        <v>2.7</v>
+      </c>
+      <c r="K28" s="16">
+        <f t="shared" si="4"/>
+        <v>0.43937234568894878</v>
+      </c>
+      <c r="L28" s="27">
+        <v>2.7</v>
+      </c>
+      <c r="M28" s="17">
+        <v>0.44700000000000001</v>
+      </c>
+      <c r="N28" s="25">
+        <v>2.7</v>
+      </c>
+      <c r="O28" s="16">
+        <v>0.47199999999999998</v>
+      </c>
+      <c r="P28" s="25">
+        <v>3.5</v>
+      </c>
+      <c r="Q28" s="5">
+        <v>0.34599999999999997</v>
+      </c>
+    </row>
+    <row r="29" spans="2:28" x14ac:dyDescent="0.4">
+      <c r="B29" s="20">
+        <v>2.15</v>
+      </c>
+      <c r="C29" s="5">
+        <f t="shared" si="0"/>
+        <v>0.65105162192761434</v>
+      </c>
+      <c r="D29" s="10">
+        <v>2.5</v>
+      </c>
+      <c r="E29" s="5">
+        <f t="shared" si="1"/>
+        <v>0.50152659551146428</v>
+      </c>
+      <c r="F29" s="10">
+        <v>2.8</v>
+      </c>
+      <c r="G29" s="16">
+        <f t="shared" si="2"/>
+        <v>0.39515163240801376</v>
+      </c>
+      <c r="H29" s="10">
+        <v>2.8</v>
+      </c>
+      <c r="I29" s="16">
+        <f t="shared" si="2"/>
+        <v>0.4000463970508964</v>
+      </c>
+      <c r="J29" s="25">
+        <v>2.8</v>
+      </c>
+      <c r="K29" s="16">
+        <f>((((1.4+1)/2)^(1.4+1)*(H29*SIN(K$5))^(2*1.4))/((1+((1.4-1)/2)*(H29*SIN(K$5))^2)^1.4*(1.4*(H29*SIN(K$5))^2-((1.4-1)/2))))^((1)/(1.4-1))</f>
+        <v>0.40473941800707208</v>
+      </c>
+      <c r="L29" s="25">
+        <v>2.8</v>
+      </c>
+      <c r="M29" s="16">
+        <f>((((1.4+1)/2)^(1.4+1)*(J29*SIN(M$5))^(2*1.4))/((1+((1.4-1)/2)*(J29*SIN(M$5))^2)^1.4*(1.4*(J29*SIN(M$5))^2-((1.4-1)/2))))^((1)/(1.4-1))</f>
+        <v>0.41033107953838149</v>
+      </c>
+      <c r="N29" s="10">
+        <v>2.8</v>
+      </c>
+      <c r="O29" s="16">
+        <v>0.42899999999999999</v>
+      </c>
+      <c r="P29" s="10">
+        <v>3.3</v>
+      </c>
+      <c r="Q29" s="5">
+        <v>0.372</v>
+      </c>
+    </row>
+    <row r="30" spans="2:28" x14ac:dyDescent="0.4">
+      <c r="B30" s="20">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C30" s="5">
+        <f t="shared" si="0"/>
+        <v>0.62813631354919564</v>
+      </c>
+      <c r="D30" s="10">
+        <v>2.6</v>
+      </c>
+      <c r="E30" s="5">
+        <f t="shared" si="1"/>
+        <v>0.46258509546384113</v>
+      </c>
+      <c r="F30" s="10">
+        <v>2.9</v>
+      </c>
+      <c r="G30" s="16">
+        <f t="shared" si="2"/>
+        <v>0.36320214652323718</v>
+      </c>
+      <c r="H30" s="10">
+        <v>2.9</v>
+      </c>
+      <c r="I30" s="16">
+        <f t="shared" si="2"/>
+        <v>0.36791373024646179</v>
+      </c>
+      <c r="J30" s="10">
+        <v>2.9</v>
+      </c>
+      <c r="K30" s="16">
+        <f t="shared" ref="K30:K36" si="5">((((1.4+1)/2)^(1.4+1)*(H30*SIN(K$5))^(2*1.4))/((1+((1.4-1)/2)*(H30*SIN(K$5))^2)^1.4*(1.4*(H30*SIN(K$5))^2-((1.4-1)/2))))^((1)/(1.4-1))</f>
+        <v>0.37243546307410436</v>
+      </c>
+      <c r="L30" s="10">
+        <v>2.9</v>
+      </c>
+      <c r="M30" s="16">
+        <f t="shared" ref="M30:O36" si="6">((((1.4+1)/2)^(1.4+1)*(J30*SIN(M$5))^(2*1.4))/((1+((1.4-1)/2)*(J30*SIN(M$5))^2)^1.4*(1.4*(J30*SIN(M$5))^2-((1.4-1)/2))))^((1)/(1.4-1))</f>
+        <v>0.37782859158380155</v>
+      </c>
+      <c r="N30" s="10">
+        <v>2.9</v>
+      </c>
+      <c r="O30" s="16">
+        <v>0.39100000000000001</v>
+      </c>
+      <c r="P30" s="10">
+        <v>3.18</v>
+      </c>
+      <c r="Q30" s="5">
+        <v>0.3805</v>
+      </c>
+    </row>
+    <row r="31" spans="2:28" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B31" s="20">
+        <v>2.25</v>
+      </c>
+      <c r="C31" s="5">
+        <f t="shared" si="0"/>
+        <v>0.60552971744757467</v>
+      </c>
+      <c r="D31" s="10">
+        <v>2.7</v>
+      </c>
+      <c r="E31" s="5">
+        <f t="shared" si="1"/>
+        <v>0.42598550959557474</v>
+      </c>
+      <c r="F31" s="10">
+        <v>3</v>
+      </c>
+      <c r="G31" s="16">
+        <f t="shared" si="2"/>
+        <v>0.33357777092578467</v>
+      </c>
+      <c r="H31" s="10">
+        <v>3</v>
+      </c>
+      <c r="I31" s="16">
+        <f t="shared" si="2"/>
+        <v>0.33809119695554091</v>
+      </c>
+      <c r="J31" s="10">
+        <v>3</v>
+      </c>
+      <c r="K31" s="16">
+        <f t="shared" si="5"/>
+        <v>0.34242665539444356</v>
+      </c>
+      <c r="L31" s="10">
+        <v>3</v>
+      </c>
+      <c r="M31" s="16">
+        <f t="shared" si="6"/>
+        <v>0.34760260361838224</v>
+      </c>
+      <c r="N31" s="27">
+        <v>3</v>
+      </c>
+      <c r="O31" s="17">
+        <v>0.35730000000000001</v>
+      </c>
+      <c r="P31" s="26">
+        <v>3.1379999999999999</v>
+      </c>
+      <c r="Q31" s="18">
+        <v>0.373</v>
+      </c>
+    </row>
+    <row r="32" spans="2:28" x14ac:dyDescent="0.4">
+      <c r="B32" s="20">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="C32" s="5">
+        <f t="shared" si="0"/>
+        <v>0.58329450812554562</v>
+      </c>
+      <c r="D32" s="10">
+        <v>2.8</v>
+      </c>
+      <c r="E32" s="5">
+        <f t="shared" si="1"/>
+        <v>0.39177898764171454</v>
+      </c>
+      <c r="F32" s="10">
+        <v>3.1</v>
+      </c>
+      <c r="G32" s="16">
+        <f t="shared" si="2"/>
+        <v>0.30619965817406303</v>
+      </c>
+      <c r="H32" s="10">
+        <v>3.1</v>
+      </c>
+      <c r="I32" s="16">
+        <f t="shared" si="2"/>
+        <v>0.31050541521127234</v>
+      </c>
+      <c r="J32" s="10">
+        <v>3.1</v>
+      </c>
+      <c r="K32" s="16">
+        <f t="shared" si="5"/>
+        <v>0.31464488394076012</v>
+      </c>
+      <c r="L32" s="10">
+        <v>3.1</v>
+      </c>
+      <c r="M32" s="16">
+        <f t="shared" si="6"/>
+        <v>0.31959132110282829</v>
+      </c>
+      <c r="N32" s="25">
+        <v>3.1</v>
+      </c>
+      <c r="O32" s="16">
+        <f t="shared" si="6"/>
+        <v>0.32749282829008969</v>
+      </c>
+      <c r="P32" s="25">
+        <v>3.15</v>
+      </c>
+      <c r="Q32" s="16">
+        <v>0.35699999999999998</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.4">
+      <c r="B33" s="20">
+        <v>2.35</v>
+      </c>
+      <c r="C33" s="5">
+        <f t="shared" si="0"/>
+        <v>0.56148422064455572</v>
+      </c>
+      <c r="D33" s="10">
+        <v>2.9</v>
+      </c>
+      <c r="E33" s="5">
+        <f t="shared" si="1"/>
+        <v>0.3599584090233614</v>
+      </c>
+      <c r="F33" s="10">
+        <v>3.2</v>
+      </c>
+      <c r="G33" s="16">
+        <f t="shared" si="2"/>
+        <v>0.2809665020476706</v>
+      </c>
+      <c r="H33" s="10">
+        <v>3.2</v>
+      </c>
+      <c r="I33" s="16">
+        <f t="shared" si="2"/>
+        <v>0.28505962089186293</v>
+      </c>
+      <c r="J33" s="10">
+        <v>3.2</v>
+      </c>
+      <c r="K33" s="16">
+        <f t="shared" si="5"/>
+        <v>0.28899778205713644</v>
+      </c>
+      <c r="L33" s="10">
+        <v>3.2</v>
+      </c>
+      <c r="M33" s="16">
+        <f t="shared" si="6"/>
+        <v>0.29370766877237847</v>
+      </c>
+      <c r="N33" s="10">
+        <v>3.2</v>
+      </c>
+      <c r="O33" s="16">
+        <f t="shared" si="6"/>
+        <v>0.30124032311619603</v>
+      </c>
+      <c r="P33" s="10">
+        <v>3.2</v>
+      </c>
+      <c r="Q33" s="16">
+        <v>0.33200000000000002</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.4">
+      <c r="B34" s="20">
+        <v>2.4</v>
+      </c>
+      <c r="C34" s="5">
+        <f t="shared" si="0"/>
+        <v>0.54014389488089332</v>
+      </c>
+      <c r="D34" s="10">
+        <v>3</v>
+      </c>
+      <c r="E34" s="5">
+        <f t="shared" si="1"/>
+        <v>0.33047286769050638</v>
+      </c>
+      <c r="F34" s="10">
+        <v>3.3</v>
+      </c>
+      <c r="G34" s="16">
+        <f t="shared" si="2"/>
+        <v>0.25776248190390483</v>
+      </c>
+      <c r="H34" s="10">
+        <v>3.3</v>
+      </c>
+      <c r="I34" s="16">
+        <f t="shared" si="2"/>
+        <v>0.2616416961413689</v>
+      </c>
+      <c r="J34" s="10">
+        <v>3.3</v>
+      </c>
+      <c r="K34" s="16">
+        <f t="shared" si="5"/>
+        <v>0.26537683152192743</v>
+      </c>
+      <c r="L34" s="10">
+        <v>3.3</v>
+      </c>
+      <c r="M34" s="16">
+        <f t="shared" si="6"/>
+        <v>0.26984747848186424</v>
+      </c>
+      <c r="N34" s="10">
+        <v>3.3</v>
+      </c>
+      <c r="O34" s="16">
+        <f t="shared" si="6"/>
+        <v>0.27700556840957719</v>
+      </c>
+      <c r="P34" s="10">
+        <v>3.3</v>
+      </c>
+      <c r="Q34" s="5">
+        <v>0.29799999999999999</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B35" s="20">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="C35" s="5">
+        <f t="shared" si="0"/>
+        <v>0.51931074139979472</v>
+      </c>
+      <c r="D35" s="10">
+        <v>3.1</v>
+      </c>
+      <c r="E35" s="5">
+        <f t="shared" si="1"/>
+        <v>0.3032397706324319</v>
+      </c>
+      <c r="F35" s="10">
+        <v>3.4</v>
+      </c>
+      <c r="G35" s="16">
+        <f t="shared" si="2"/>
+        <v>0.23646349585475601</v>
+      </c>
+      <c r="H35" s="10">
+        <v>3.4</v>
+      </c>
+      <c r="I35" s="16">
+        <f t="shared" si="2"/>
+        <v>0.2401304976683529</v>
+      </c>
+      <c r="J35" s="10">
+        <v>3.4</v>
+      </c>
+      <c r="K35" s="16">
+        <f t="shared" si="5"/>
+        <v>0.24366377826453306</v>
+      </c>
+      <c r="L35" s="10">
+        <v>3.4</v>
+      </c>
+      <c r="M35" s="16">
+        <f t="shared" si="6"/>
+        <v>0.24789600420801144</v>
+      </c>
+      <c r="N35" s="10">
+        <v>3.4</v>
+      </c>
+      <c r="O35" s="16">
+        <f t="shared" si="6"/>
+        <v>0.25467954157828859</v>
+      </c>
+      <c r="P35" s="27">
+        <v>3.4</v>
+      </c>
+      <c r="Q35" s="17">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="36" spans="2:17" x14ac:dyDescent="0.4">
+      <c r="B36" s="20">
+        <v>2.5</v>
+      </c>
+      <c r="C36" s="5">
+        <f t="shared" si="0"/>
+        <v>0.49901481202915121</v>
+      </c>
+      <c r="D36" s="10">
+        <v>3.2</v>
+      </c>
+      <c r="E36" s="5">
+        <f t="shared" si="1"/>
+        <v>0.27815470942422532</v>
+      </c>
+      <c r="F36" s="10">
+        <v>3.5</v>
+      </c>
+      <c r="G36" s="16">
+        <f t="shared" si="2"/>
+        <v>0.21694194788937024</v>
+      </c>
+      <c r="H36" s="10">
+        <v>3.5</v>
+      </c>
+      <c r="I36" s="16">
+        <f t="shared" si="2"/>
+        <v>0.22040074148669114</v>
+      </c>
+      <c r="J36" s="10">
+        <v>3.5</v>
+      </c>
+      <c r="K36" s="16">
+        <f t="shared" si="5"/>
+        <v>0.22373560792157701</v>
+      </c>
+      <c r="L36" s="10">
+        <v>3.5</v>
+      </c>
+      <c r="M36" s="16">
+        <f t="shared" si="6"/>
+        <v>0.22773300220591197</v>
+      </c>
+      <c r="N36" s="10">
+        <v>3.5</v>
+      </c>
+      <c r="O36" s="16">
+        <f t="shared" si="6"/>
+        <v>0.23414655206576382</v>
+      </c>
+      <c r="P36" s="25">
+        <v>3.5</v>
+      </c>
+      <c r="Q36" s="16">
+        <f t="shared" ref="Q36" si="7">((((1.4+1)/2)^(1.4+1)*(P36*SIN(Q$5))^(2*1.4))/((1+((1.4-1)/2)*(P36*SIN(Q$5))^2)^1.4*(1.4*(P36*SIN(Q$5))^2-((1.4-1)/2))))^((1)/(1.4-1))</f>
+        <v>0.24627140920000326</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.4">
+      <c r="B37" s="20">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="C37" s="5">
+        <f t="shared" si="0"/>
+        <v>0.47927966180462583</v>
+      </c>
+      <c r="D37" s="10">
+        <v>3.3</v>
+      </c>
+      <c r="E37" s="5">
+        <f t="shared" si="1"/>
+        <v>0.25509934359305275</v>
+      </c>
+      <c r="F37" s="10"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="10"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="10"/>
+      <c r="K37" s="5"/>
+      <c r="L37" s="10"/>
+      <c r="M37" s="16"/>
+      <c r="N37" s="10"/>
+      <c r="O37" s="5"/>
+      <c r="P37" s="10"/>
+      <c r="Q37" s="5"/>
+    </row>
+    <row r="38" spans="2:17" x14ac:dyDescent="0.4">
+      <c r="B38" s="20">
+        <v>2.6</v>
+      </c>
+      <c r="C38" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4601229920348951</v>
+      </c>
+      <c r="D38" s="10">
+        <v>3.4</v>
+      </c>
+      <c r="E38" s="5">
+        <f t="shared" si="1"/>
+        <v>0.23394756592546659</v>
+      </c>
+      <c r="F38" s="10"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="10"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="10"/>
+      <c r="K38" s="5"/>
+      <c r="L38" s="10"/>
+      <c r="M38" s="5"/>
+      <c r="N38" s="10"/>
+      <c r="O38" s="5"/>
+      <c r="P38" s="10"/>
+      <c r="Q38" s="5"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.4">
+      <c r="B39" s="20">
+        <v>2.65</v>
+      </c>
+      <c r="C39" s="5">
+        <f t="shared" si="0"/>
+        <v>0.44155726684386321</v>
+      </c>
+      <c r="D39" s="10">
+        <v>3.5</v>
+      </c>
+      <c r="E39" s="5">
+        <f t="shared" si="1"/>
+        <v>0.21457022062792372</v>
+      </c>
+      <c r="F39" s="10"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="10"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="10"/>
+      <c r="K39" s="5"/>
+      <c r="L39" s="10"/>
+      <c r="M39" s="5"/>
+      <c r="N39" s="10"/>
+      <c r="O39" s="5"/>
+      <c r="P39" s="10"/>
+      <c r="Q39" s="5"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.4">
+      <c r="B40" s="20">
+        <v>2.7</v>
+      </c>
+      <c r="C40" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4235902977319202</v>
+      </c>
+      <c r="D40" s="10"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="10"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="10"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="10"/>
+      <c r="K40" s="5"/>
+      <c r="L40" s="10"/>
+      <c r="M40" s="5"/>
+      <c r="N40" s="10"/>
+      <c r="O40" s="5"/>
+      <c r="P40" s="10"/>
+      <c r="Q40" s="5"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.4">
+      <c r="B41" s="20">
+        <v>2.75</v>
+      </c>
+      <c r="C41" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4062257925068673</v>
+      </c>
+      <c r="D41" s="10"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="10"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="10"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="10"/>
+      <c r="K41" s="5"/>
+      <c r="L41" s="10"/>
+      <c r="M41" s="5"/>
+      <c r="N41" s="10"/>
+      <c r="O41" s="5"/>
+      <c r="P41" s="10"/>
+      <c r="Q41" s="5"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.4">
+      <c r="B42" s="20">
+        <v>2.8</v>
+      </c>
+      <c r="C42" s="5">
+        <f t="shared" si="0"/>
+        <v>0.38946386641192116</v>
+      </c>
+      <c r="D42" s="10"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="10"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="10"/>
+      <c r="I42" s="5"/>
+      <c r="J42" s="10"/>
+      <c r="K42" s="5"/>
+      <c r="L42" s="10"/>
+      <c r="M42" s="5"/>
+      <c r="N42" s="10"/>
+      <c r="O42" s="5"/>
+      <c r="P42" s="10"/>
+      <c r="Q42" s="5"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.4">
+      <c r="B43" s="20">
+        <v>2.85</v>
+      </c>
+      <c r="C43" s="5">
+        <f t="shared" si="0"/>
+        <v>0.37330151446622861</v>
+      </c>
+      <c r="D43" s="10"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="10"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="10"/>
+      <c r="I43" s="5"/>
+      <c r="J43" s="10"/>
+      <c r="K43" s="5"/>
+      <c r="L43" s="10"/>
+      <c r="M43" s="5"/>
+      <c r="N43" s="10"/>
+      <c r="O43" s="5"/>
+      <c r="P43" s="10"/>
+      <c r="Q43" s="5"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.4">
+      <c r="B44" s="20">
+        <v>2.9</v>
+      </c>
+      <c r="C44" s="5">
+        <f t="shared" si="0"/>
+        <v>0.35773304497254471</v>
+      </c>
+      <c r="D44" s="10"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="10"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="10"/>
+      <c r="I44" s="5"/>
+      <c r="J44" s="10"/>
+      <c r="K44" s="5"/>
+      <c r="L44" s="10"/>
+      <c r="M44" s="5"/>
+      <c r="N44" s="10"/>
+      <c r="O44" s="5"/>
+      <c r="P44" s="10"/>
+      <c r="Q44" s="5"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.4">
+      <c r="B45" s="20">
+        <v>2.95</v>
+      </c>
+      <c r="C45" s="5">
+        <f t="shared" si="0"/>
+        <v>0.34275047487402643</v>
+      </c>
+      <c r="D45" s="10"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="10"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="10"/>
+      <c r="I45" s="5"/>
+      <c r="J45" s="10"/>
+      <c r="K45" s="5"/>
+      <c r="L45" s="10"/>
+      <c r="M45" s="5"/>
+      <c r="N45" s="10"/>
+      <c r="O45" s="5"/>
+      <c r="P45" s="10"/>
+      <c r="Q45" s="5"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.4">
+      <c r="B46" s="20">
+        <v>3</v>
+      </c>
+      <c r="C46" s="5">
+        <f t="shared" si="0"/>
+        <v>0.32834388819073695</v>
+      </c>
+      <c r="D46" s="10"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="10"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="10"/>
+      <c r="I46" s="5"/>
+      <c r="J46" s="10"/>
+      <c r="K46" s="5"/>
+      <c r="L46" s="10"/>
+      <c r="M46" s="5"/>
+      <c r="N46" s="10"/>
+      <c r="O46" s="5"/>
+      <c r="P46" s="10"/>
+      <c r="Q46" s="5"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.4">
+      <c r="B47" s="20">
+        <v>3.05</v>
+      </c>
+      <c r="C47" s="5">
+        <f t="shared" si="0"/>
+        <v>0.3145017591661417</v>
+      </c>
+      <c r="D47" s="10"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="10"/>
+      <c r="G47" s="5"/>
+      <c r="H47" s="10"/>
+      <c r="I47" s="13"/>
+      <c r="J47" s="10"/>
+      <c r="K47" s="13"/>
+      <c r="L47" s="10"/>
+      <c r="M47" s="13"/>
+      <c r="N47" s="10"/>
+      <c r="O47" s="13"/>
+      <c r="P47" s="10"/>
+      <c r="Q47" s="13"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.4">
+      <c r="B48" s="20">
+        <v>3.1</v>
+      </c>
+      <c r="C48" s="5">
+        <f t="shared" si="0"/>
+        <v>0.30121124203081562</v>
+      </c>
+      <c r="D48" s="10"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="10"/>
+      <c r="G48" s="5"/>
+      <c r="H48" s="10"/>
+      <c r="I48" s="13"/>
+      <c r="J48" s="10"/>
+      <c r="K48" s="13"/>
+      <c r="L48" s="10"/>
+      <c r="M48" s="13"/>
+      <c r="N48" s="10"/>
+      <c r="O48" s="13"/>
+      <c r="P48" s="10"/>
+      <c r="Q48" s="13"/>
+    </row>
+    <row r="49" spans="2:17" x14ac:dyDescent="0.4">
+      <c r="B49" s="20">
+        <v>3.15</v>
+      </c>
+      <c r="C49" s="5">
+        <f t="shared" si="0"/>
+        <v>0.28845842946759725</v>
+      </c>
+      <c r="D49" s="10"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="10"/>
+      <c r="G49" s="5"/>
+      <c r="H49" s="10"/>
+      <c r="I49" s="13"/>
+      <c r="J49" s="10"/>
+      <c r="K49" s="13"/>
+      <c r="L49" s="10"/>
+      <c r="M49" s="13"/>
+      <c r="N49" s="10"/>
+      <c r="O49" s="13"/>
+      <c r="P49" s="10"/>
+      <c r="Q49" s="13"/>
+    </row>
+    <row r="50" spans="2:17" x14ac:dyDescent="0.4">
+      <c r="B50" s="20">
+        <v>3.2</v>
+      </c>
+      <c r="C50" s="5">
+        <f t="shared" si="0"/>
+        <v>0.27622858195917344</v>
+      </c>
+      <c r="D50" s="10"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="10"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="10"/>
+      <c r="I50" s="13"/>
+      <c r="J50" s="10"/>
+      <c r="K50" s="13"/>
+      <c r="L50" s="10"/>
+      <c r="M50" s="13"/>
+      <c r="N50" s="10"/>
+      <c r="O50" s="13"/>
+      <c r="P50" s="10"/>
+      <c r="Q50" s="13"/>
+    </row>
+    <row r="51" spans="2:17" x14ac:dyDescent="0.4">
+      <c r="B51" s="20">
+        <v>3.25</v>
+      </c>
+      <c r="C51" s="5">
+        <f t="shared" si="0"/>
+        <v>0.26450633023243536</v>
+      </c>
+      <c r="D51" s="10"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="10"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="10"/>
+      <c r="I51" s="13"/>
+      <c r="J51" s="10"/>
+      <c r="K51" s="13"/>
+      <c r="L51" s="10"/>
+      <c r="M51" s="13"/>
+      <c r="N51" s="10"/>
+      <c r="O51" s="13"/>
+      <c r="P51" s="10"/>
+      <c r="Q51" s="13"/>
+    </row>
+    <row r="52" spans="2:17" x14ac:dyDescent="0.4">
+      <c r="B52" s="20">
+        <v>3.3</v>
+      </c>
+      <c r="C52" s="5">
+        <f t="shared" si="0"/>
+        <v>0.25327585299801569</v>
+      </c>
+      <c r="D52" s="10"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="10"/>
+      <c r="G52" s="5"/>
+      <c r="H52" s="10"/>
+      <c r="I52" s="13"/>
+      <c r="J52" s="10"/>
+      <c r="K52" s="13"/>
+      <c r="L52" s="10"/>
+      <c r="M52" s="13"/>
+      <c r="N52" s="10"/>
+      <c r="O52" s="13"/>
+      <c r="P52" s="10"/>
+      <c r="Q52" s="13"/>
+    </row>
+    <row r="53" spans="2:17" x14ac:dyDescent="0.4">
+      <c r="B53" s="20">
+        <v>3.35</v>
+      </c>
+      <c r="C53" s="5">
+        <f t="shared" si="0"/>
+        <v>0.24252103213017481</v>
+      </c>
+      <c r="D53" s="10"/>
+      <c r="E53" s="5"/>
+      <c r="F53" s="10"/>
+      <c r="G53" s="5"/>
+      <c r="H53" s="10"/>
+      <c r="I53" s="13"/>
+      <c r="J53" s="10"/>
+      <c r="K53" s="13"/>
+      <c r="L53" s="10"/>
+      <c r="M53" s="13"/>
+      <c r="N53" s="10"/>
+      <c r="O53" s="13"/>
+      <c r="P53" s="10"/>
+      <c r="Q53" s="13"/>
+    </row>
+    <row r="54" spans="2:17" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="B54" s="20">
+        <v>3.4</v>
+      </c>
+      <c r="C54" s="5">
+        <f t="shared" si="0"/>
+        <v>0.23222558735142332</v>
+      </c>
+      <c r="D54" s="10"/>
+      <c r="E54" s="5"/>
+      <c r="F54" s="10"/>
+      <c r="G54" s="5"/>
+      <c r="H54" s="10"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="10"/>
+      <c r="K54" s="13"/>
+      <c r="L54" s="10"/>
+      <c r="M54" s="13"/>
+      <c r="N54" s="10"/>
+      <c r="O54" s="13"/>
+      <c r="P54" s="10"/>
+      <c r="Q54" s="13"/>
+    </row>
+    <row r="55" spans="2:17" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="B55" s="20">
+        <v>3.45</v>
+      </c>
+      <c r="C55" s="5">
+        <f t="shared" si="0"/>
+        <v>0.22237319238607181</v>
+      </c>
+      <c r="D55" s="10"/>
+      <c r="E55" s="5"/>
+      <c r="F55" s="10"/>
+      <c r="G55" s="5"/>
+      <c r="H55" s="10"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="10"/>
+      <c r="K55" s="13"/>
+      <c r="L55" s="10"/>
+      <c r="M55" s="13"/>
+      <c r="N55" s="10"/>
+      <c r="O55" s="13"/>
+      <c r="P55" s="10"/>
+      <c r="Q55" s="13"/>
+    </row>
+    <row r="56" spans="2:17" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="B56" s="20">
+        <v>3.5</v>
+      </c>
+      <c r="C56" s="5">
+        <f t="shared" si="0"/>
+        <v>0.2129475744338053</v>
+      </c>
+      <c r="D56" s="10"/>
+      <c r="E56" s="5"/>
+      <c r="F56" s="10"/>
+      <c r="G56" s="5"/>
+      <c r="H56" s="10"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="10"/>
+      <c r="K56" s="13"/>
+      <c r="L56" s="10"/>
+      <c r="M56" s="13"/>
+      <c r="N56" s="10"/>
+      <c r="O56" s="13"/>
+      <c r="P56" s="10"/>
+      <c r="Q56" s="13"/>
+    </row>
+    <row r="57" spans="2:17" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B57" s="22"/>
+      <c r="D57" s="28"/>
+      <c r="F57" s="28"/>
+      <c r="H57" s="28"/>
+      <c r="J57" s="28"/>
+      <c r="L57" s="28"/>
+      <c r="N57" s="28"/>
+      <c r="P57" s="28"/>
+    </row>
+    <row r="58" spans="2:17" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B58" s="22"/>
+      <c r="D58" s="28"/>
+      <c r="F58" s="28"/>
+      <c r="H58" s="28"/>
+      <c r="J58" s="28"/>
+      <c r="L58" s="28"/>
+      <c r="N58" s="28"/>
+      <c r="P58" s="28"/>
+    </row>
+    <row r="59" spans="2:17" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B59" s="22"/>
+      <c r="D59" s="28"/>
+      <c r="F59" s="28"/>
+      <c r="H59" s="28"/>
+      <c r="J59" s="28"/>
+      <c r="L59" s="28"/>
+      <c r="N59" s="28"/>
+      <c r="P59" s="28"/>
+    </row>
+    <row r="60" spans="2:17" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B60" s="22"/>
+      <c r="D60" s="28"/>
+      <c r="F60" s="28"/>
+      <c r="H60" s="28"/>
+      <c r="J60" s="28"/>
+      <c r="L60" s="28"/>
+      <c r="N60" s="28"/>
+      <c r="P60" s="28"/>
+    </row>
+    <row r="61" spans="2:17" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B61" s="22"/>
+      <c r="D61" s="28"/>
+      <c r="F61" s="28"/>
+      <c r="H61" s="28"/>
+      <c r="J61" s="28"/>
+      <c r="L61" s="28"/>
+      <c r="N61" s="28"/>
+      <c r="P61" s="28"/>
+    </row>
+    <row r="62" spans="2:17" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B62" s="22"/>
+      <c r="D62" s="28"/>
+      <c r="F62" s="28"/>
+      <c r="H62" s="28"/>
+      <c r="J62" s="28"/>
+      <c r="L62" s="28"/>
+      <c r="N62" s="28"/>
+      <c r="P62" s="28"/>
+    </row>
+    <row r="63" spans="2:17" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B63" s="22"/>
+      <c r="D63" s="28"/>
+      <c r="F63" s="28"/>
+      <c r="H63" s="28"/>
+      <c r="J63" s="28"/>
+      <c r="L63" s="28"/>
+      <c r="N63" s="28"/>
+      <c r="P63" s="28"/>
+    </row>
+    <row r="64" spans="2:17" x14ac:dyDescent="0.4">
+      <c r="D64" s="28"/>
+    </row>
+    <row r="65" spans="4:4" x14ac:dyDescent="0.4">
+      <c r="D65" s="28"/>
+    </row>
+    <row r="66" spans="4:4" x14ac:dyDescent="0.4">
+      <c r="D66" s="28"/>
+    </row>
+    <row r="67" spans="4:4" x14ac:dyDescent="0.4">
+      <c r="D67" s="28"/>
+    </row>
+    <row r="68" spans="4:4" x14ac:dyDescent="0.4">
+      <c r="D68" s="28"/>
+    </row>
+    <row r="69" spans="4:4" x14ac:dyDescent="0.4">
+      <c r="D69" s="28"/>
+    </row>
+    <row r="70" spans="4:4" x14ac:dyDescent="0.4">
+      <c r="D70" s="28"/>
+    </row>
+    <row r="71" spans="4:4" x14ac:dyDescent="0.4">
+      <c r="D71" s="28"/>
+    </row>
+    <row r="72" spans="4:4" x14ac:dyDescent="0.4">
+      <c r="D72" s="28"/>
+    </row>
+    <row r="73" spans="4:4" x14ac:dyDescent="0.4">
+      <c r="D73" s="28"/>
+    </row>
+    <row r="74" spans="4:4" x14ac:dyDescent="0.4">
+      <c r="D74" s="28"/>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="H2:H5"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="J2:J5"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="L2:L5"/>
+    <mergeCell ref="N2:N5"/>
+    <mergeCell ref="P2:P5"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F2:F5"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="D2:D5"/>
+    <mergeCell ref="B2:B5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/Strömungslehre 2/images/SL2-Diagrams.xlsx
+++ b/Strömungslehre 2/images/SL2-Diagrams.xlsx
@@ -8,31 +8,39 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Phillip\Documents\Git\Project-FoSa\Strömungslehre 2\images\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E570561-F534-4684-9540-3A1EFD6A82F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{148D0EC5-66C2-4F8E-B3CB-A9CFB74806C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="46296" windowHeight="18696" activeTab="3" xr2:uid="{FA5394E7-ED4E-4AC0-A8BA-0A137B0856E0}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="46296" windowHeight="18696" activeTab="4" xr2:uid="{FA5394E7-ED4E-4AC0-A8BA-0A137B0856E0}"/>
   </bookViews>
   <sheets>
     <sheet name="Adiabate-Vorgänge" sheetId="4" r:id="rId1"/>
     <sheet name="xliv" sheetId="1" r:id="rId2"/>
     <sheet name="xlv" sheetId="3" r:id="rId3"/>
     <sheet name="xlvi" sheetId="5" r:id="rId4"/>
+    <sheet name="xlvii" sheetId="7" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="solver_eng" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_eng" localSheetId="3" hidden="1">1</definedName>
+    <definedName name="solver_eng" localSheetId="4" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="3" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="4" hidden="1">1</definedName>
     <definedName name="solver_num" localSheetId="2" hidden="1">0</definedName>
     <definedName name="solver_num" localSheetId="3" hidden="1">0</definedName>
+    <definedName name="solver_num" localSheetId="4" hidden="1">0</definedName>
     <definedName name="solver_opt" localSheetId="2" hidden="1">xlv!$D$5</definedName>
     <definedName name="solver_opt" localSheetId="3" hidden="1">xlvi!#REF!</definedName>
+    <definedName name="solver_opt" localSheetId="4" hidden="1">xlvii!#REF!</definedName>
     <definedName name="solver_typ" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_typ" localSheetId="3" hidden="1">1</definedName>
+    <definedName name="solver_typ" localSheetId="4" hidden="1">1</definedName>
     <definedName name="solver_val" localSheetId="2" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="3" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="4" hidden="1">0</definedName>
     <definedName name="solver_ver" localSheetId="2" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="3" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="4" hidden="1">3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -55,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="16">
   <si>
     <t>DEG</t>
   </si>
@@ -117,6 +125,56 @@
   <si>
     <t>Druckverh.</t>
   </si>
+  <si>
+    <r>
+      <t>Ma</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="CMU Serif"/>
+      </rPr>
+      <t>1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Ma</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="CMU Serif"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Ma</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="CMU Serif"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="CMU Serif"/>
+      </rPr>
+      <t xml:space="preserve"> lin.</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -130,7 +188,7 @@
     <numFmt numFmtId="168" formatCode="0.0000"/>
     <numFmt numFmtId="169" formatCode="&quot;→ σ = &quot;0.000"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -162,6 +220,12 @@
     <font>
       <sz val="11"/>
       <color theme="0" tint="-0.499984740745262"/>
+      <name val="CMU Serif"/>
+    </font>
+    <font>
+      <vertAlign val="subscript"/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="CMU Serif"/>
     </font>
   </fonts>
@@ -351,7 +415,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -421,6 +485,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -471,6 +538,18 @@
     </xf>
     <xf numFmtId="2" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -13401,7 +13480,7 @@
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                   </a:rPr>
-                  <a:t>Diagramm xlvi                                                    Ma</a:t>
+                  <a:t>Diagramm xlvi                                                        Ma</a:t>
                 </a:r>
                 <a:r>
                   <a:rPr lang="de-DE" baseline="-25000">
@@ -13659,6 +13738,1682 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="de-DE"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="9.2809469266555394E-2"/>
+          <c:y val="1.4263741923879563E-2"/>
+          <c:w val="0.881440611002694"/>
+          <c:h val="0.92613323210196863"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>θ = 0°, oben</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="15875" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>xlvii!$B$5:$B$30</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="26"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.1000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.1</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.2000000000000002</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.2999999999999998</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.4</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.6</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.7</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.8</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2.9</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>3.1</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>3.2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>3.3</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>3.4</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>3.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>xlvii!$B$5:$B$30</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="26"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.1000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.1</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.2000000000000002</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.2999999999999998</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.4</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.6</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.7</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.8</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2.9</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>3.1</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>3.2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>3.3</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>3.4</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>3.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000A-6B71-4DBA-B5B2-FECB29A98B64}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>θ = 0°, unten</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="15875" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>xlvii!$C$5:$C$30</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="26"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.1000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.2000000000000002</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.4</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.63</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>xlvii!$D$5:$D$30</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="26"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.91</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.84199999999999997</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.78600000000000003</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.74</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.70199999999999996</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.66800000000000004</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.61599999999999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.57799999999999996</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.54800000000000004</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.52500000000000002</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000B-6B71-4DBA-B5B2-FECB29A98B64}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>xlvii!$E$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>θ = 5°</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="15875" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>xlvii!$E$5:$E$30</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="26"/>
+                <c:pt idx="0">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.4</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.24</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.4</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.6</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.7</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.67</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>xlvii!$F$5:$F$30</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="26"/>
+                <c:pt idx="0">
+                  <c:v>3.2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.75</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.2999999999999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.825</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.327</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.22</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.0900000000000001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.83299999999999996</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.76500000000000001</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.72</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.68300000000000005</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.65200000000000002</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.58499999999999996</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.52</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-DDDF-4FBC-B281-9D2F0431BB15}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>xlvii!$G$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>θ = 10°</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="15875" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>xlvii!$G$5:$G$30</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="26"/>
+                <c:pt idx="0">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.7</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.42</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.6</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.7</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.8250000000000002</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>xlvii!$H$5:$H$30</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="26"/>
+                <c:pt idx="0">
+                  <c:v>2.9049999999999998</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.5099999999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.0880000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.6439999999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.35</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.24</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.1180000000000001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.92400000000000004</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.78500000000000003</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.72399999999999998</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.68600000000000005</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.60399999999999998</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.53500000000000003</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-53F3-4101-B09D-E28FEAB8143E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>xlvii!$I$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>θ = 15°</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="15875" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>xlvii!$I$5:$I$30</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="26"/>
+                <c:pt idx="0">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.8</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.6120000000000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.7</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.8</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.6</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3.1120000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>xlvii!$J$5:$J$30</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="26"/>
+                <c:pt idx="0">
+                  <c:v>2.61</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.2599999999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.875</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.45</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.35</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.2490000000000001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.123</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.92500000000000004</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.77</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.71199999999999997</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.64400000000000002</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.54800000000000004</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-53F3-4101-B09D-E28FEAB8143E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>xlvii!$K$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>θ = 20°</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="15875" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>xlvii!$K$5:$K$30</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="26"/>
+                <c:pt idx="0">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.2000000000000002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.9</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.84</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.2000000000000002</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>xlvii!$L$5:$L$30</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="26"/>
+                <c:pt idx="0">
+                  <c:v>2.2999999999999998</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.9930000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.6479999999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.4059999999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.21</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.083</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.91400000000000003</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.78800000000000003</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.73</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.65600000000000003</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.59599999999999997</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.54200000000000004</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.51200000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-53F3-4101-B09D-E28FEAB8143E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>xlvii!$M$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>θ = 25°</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="15875" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>xlvii!$M$5:$M$30</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="26"/>
+                <c:pt idx="0">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.9</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.2000000000000002</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.125</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.2000000000000002</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.6</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.9</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3.2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>xlvii!$N$5:$N$30</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="26"/>
+                <c:pt idx="0">
+                  <c:v>1.9830000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.83</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.66</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.4650000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.31</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.1120000000000001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.93</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.79600000000000004</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.69799999999999995</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.60499999999999998</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.56999999999999995</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.54900000000000004</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-53F3-4101-B09D-E28FEAB8143E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>xlvii!$O$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>θ = 30°</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="15875" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>xlvii!$O$5:$O$30</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="26"/>
+                <c:pt idx="0">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.9</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.52</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>xlvii!$P$5:$P$30</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="26"/>
+                <c:pt idx="0">
+                  <c:v>1.657</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.516</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.3460000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.21</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.1180000000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.94499999999999995</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.81200000000000006</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.75800000000000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.69599999999999995</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.64500000000000002</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.61199999999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-53F3-4101-B09D-E28FEAB8143E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="8"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>xlvii!$Q$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>θ = 35°</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="15875" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>xlvii!$Q$5:$Q$30</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="26"/>
+                <c:pt idx="0">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.1440000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>xlvii!$R$5:$R$30</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="26"/>
+                <c:pt idx="0">
+                  <c:v>1.268</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.1559999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.073</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.95699999999999996</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.86199999999999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.81200000000000006</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.753</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-53F3-4101-B09D-E28FEAB8143E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1903764384"/>
+        <c:axId val="1903764864"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1903764384"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="3.5"/>
+          <c:min val="1"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                    <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                    <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="de-DE">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Diagramm xlvii                                                   Ma</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="de-DE" baseline="-25000">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>1</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="de-DE" i="1">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>  </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="de-DE" i="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>[</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="de-DE" sz="500" i="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t> </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="de-DE" i="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>-</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="de-DE" sz="500" i="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t> </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="de-DE" i="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>]</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="2.1526300317190154E-2"/>
+              <c:y val="0.96747213521891962"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                  <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                  <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="de-DE"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1903764864"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="0.2"/>
+        <c:minorUnit val="5.000000000000001E-2"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1903764864"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="3.5"/>
+          <c:min val="0.5"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="65000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                    <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                    <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Ma</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="-25000">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>2</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>  [</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="500">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t> </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>-</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="500">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t> </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>]</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="1.2688085227411192E-2"/>
+              <c:y val="0.47254197805668863"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                  <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                  <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="de-DE"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1903764384"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="0.1"/>
+        <c:minorUnit val="5.000000000000001E-2"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="rnd" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="bg1">
+          <a:lumMod val="65000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+          <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+          <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="de-DE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.7" r="0.7" t="0.78740157499999996" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -13780,6 +15535,46 @@
 </file>
 
 <file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -15368,6 +17163,522 @@
 </file>
 
 <file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -22083,6 +24394,1968 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>3199</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>2450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>279251</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>197126</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="18" name="Gruppieren 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D5D9DF6-6F61-03F8-A231-FDA0F9F9B8E6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="16561459" y="200570"/>
+          <a:ext cx="6615892" cy="9704436"/>
+          <a:chOff x="16561459" y="200570"/>
+          <a:chExt cx="6615892" cy="9704436"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:graphicFrame macro="">
+        <xdr:nvGraphicFramePr>
+          <xdr:cNvPr id="3" name="Diagramm 2">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5567AA6B-F90E-5AC0-A8A5-15EBB7CBE5D8}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGraphicFramePr/>
+        </xdr:nvGraphicFramePr>
+        <xdr:xfrm>
+          <a:off x="16561459" y="200570"/>
+          <a:ext cx="6615892" cy="9704436"/>
+        </xdr:xfrm>
+        <a:graphic>
+          <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+            <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          </a:graphicData>
+        </a:graphic>
+      </xdr:graphicFrame>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="2" name="Textfeld 24">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A152C67-C597-4E23-9131-A3DDB4E9809F}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="21206460" y="6598920"/>
+            <a:ext cx="471001" cy="300179"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr wrap="square" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle>
+            <a:lvl1pPr marL="0" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="de-DE" sz="1100" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t>30°</a:t>
+            </a:r>
+            <a:endParaRPr lang="de-DE" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="4" name="Textfeld 24">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9C85307-4539-4398-8316-28B75DFA7952}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="22151340" y="7162800"/>
+            <a:ext cx="471001" cy="300179"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr wrap="square" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle>
+            <a:lvl1pPr marL="0" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="de-DE" sz="1100" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t>35°</a:t>
+            </a:r>
+            <a:endParaRPr lang="de-DE" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="5" name="Textfeld 24">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A9FE496-50FE-460D-9089-FD29585D31E1}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="20543520" y="6210300"/>
+            <a:ext cx="471001" cy="300179"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr wrap="square" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle>
+            <a:lvl1pPr marL="0" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="de-DE" sz="1100" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t>25°</a:t>
+            </a:r>
+            <a:endParaRPr lang="de-DE" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="6" name="Textfeld 24">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF74AB73-9BC4-4FA9-90B4-9A419C7E7B9C}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="20025360" y="5958840"/>
+            <a:ext cx="471001" cy="300179"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr wrap="square" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle>
+            <a:lvl1pPr marL="0" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="de-DE" sz="1100" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t>20°</a:t>
+            </a:r>
+            <a:endParaRPr lang="de-DE" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="7" name="Textfeld 24">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B6111DA-DF22-4C03-B65E-37EA97A033DE}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="19621500" y="5730240"/>
+            <a:ext cx="471001" cy="300179"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr wrap="square" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle>
+            <a:lvl1pPr marL="0" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="de-DE" sz="1100" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t>15°</a:t>
+            </a:r>
+            <a:endParaRPr lang="de-DE" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="8" name="Textfeld 24">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8893CAA-6DEC-4FA1-B95A-2E3A55DD8A3A}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="19293840" y="5524500"/>
+            <a:ext cx="471001" cy="300179"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr wrap="square" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle>
+            <a:lvl1pPr marL="0" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="de-DE" sz="1100" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t>10°</a:t>
+            </a:r>
+            <a:endParaRPr lang="de-DE" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="9" name="Textfeld 24">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A4BE7D5-F9F6-44F4-84DF-279BAE1F5903}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="19004280" y="5341620"/>
+            <a:ext cx="471001" cy="300179"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr wrap="square" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle>
+            <a:lvl1pPr marL="0" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="de-DE" sz="1100" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t>5°</a:t>
+            </a:r>
+            <a:endParaRPr lang="de-DE" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="10" name="Textfeld 9">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73D8F29F-DD29-4E4F-990A-C96068602CB1}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm rot="18477054">
+            <a:off x="17952720" y="5158740"/>
+            <a:ext cx="1921549" cy="301892"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="de-DE" sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t>Ablenkungswinkel</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="de-DE" sz="1100" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t> </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="el-GR" sz="1100" i="1" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Latin Modern Math" panose="02000503000000000000" pitchFamily="50" charset="0"/>
+                <a:ea typeface="Latin Modern Math" panose="02000503000000000000" pitchFamily="50" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t>ϑ</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="de-DE" sz="1100" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t> = 0°</a:t>
+            </a:r>
+            <a:endParaRPr lang="de-DE" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="11" name="Textfeld 24">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21577BAC-D805-4593-B7C0-2A34A8E6A120}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="18685329" y="3635614"/>
+            <a:ext cx="1766096" cy="299926"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr wrap="square" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle>
+            <a:lvl1pPr marL="0" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="de-DE" sz="1100" i="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t>Mach-Welle</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="12" name="Freihandform: Form 11">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C1334FAA-6303-461F-906B-60B0B4190005}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm rot="14170998">
+            <a:off x="20006003" y="3794574"/>
+            <a:ext cx="205252" cy="95571"/>
+          </a:xfrm>
+          <a:custGeom>
+            <a:avLst/>
+            <a:gdLst>
+              <a:gd name="csX0" fmla="*/ 0 w 321013"/>
+              <a:gd name="csY0" fmla="*/ 259404 h 259404"/>
+              <a:gd name="csX1" fmla="*/ 175098 w 321013"/>
+              <a:gd name="csY1" fmla="*/ 201038 h 259404"/>
+              <a:gd name="csX2" fmla="*/ 321013 w 321013"/>
+              <a:gd name="csY2" fmla="*/ 0 h 259404"/>
+            </a:gdLst>
+            <a:ahLst/>
+            <a:cxnLst>
+              <a:cxn ang="0">
+                <a:pos x="csX0" y="csY0"/>
+              </a:cxn>
+              <a:cxn ang="0">
+                <a:pos x="csX1" y="csY1"/>
+              </a:cxn>
+              <a:cxn ang="0">
+                <a:pos x="csX2" y="csY2"/>
+              </a:cxn>
+            </a:cxnLst>
+            <a:rect l="l" t="t" r="r" b="b"/>
+            <a:pathLst>
+              <a:path w="321013" h="259404">
+                <a:moveTo>
+                  <a:pt x="0" y="259404"/>
+                </a:moveTo>
+                <a:cubicBezTo>
+                  <a:pt x="60798" y="251838"/>
+                  <a:pt x="121596" y="244272"/>
+                  <a:pt x="175098" y="201038"/>
+                </a:cubicBezTo>
+                <a:cubicBezTo>
+                  <a:pt x="228600" y="157804"/>
+                  <a:pt x="284805" y="64851"/>
+                  <a:pt x="321013" y="0"/>
+                </a:cubicBezTo>
+              </a:path>
+            </a:pathLst>
+          </a:custGeom>
+          <a:noFill/>
+          <a:ln w="12700" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent5">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="de-DE" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="14" name="Textfeld 24">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7BB71C8C-24A1-2588-FC0A-99B898BB14EF}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="17193986" y="2133600"/>
+            <a:ext cx="1756074" cy="297933"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr wrap="square" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle>
+            <a:lvl1pPr marL="0" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="el-GR" sz="1100" i="1" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Latin Modern Math" panose="02000503000000000000" pitchFamily="50" charset="0"/>
+                <a:ea typeface="Latin Modern Math" panose="02000503000000000000" pitchFamily="50" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t>ϑ</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="de-DE" sz="1100" i="0" baseline="-25000">
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t>max</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="de-DE" sz="1100" i="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t> liegt bei Ma</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="de-DE" sz="1100" i="0" baseline="-25000">
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t>1,min</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="15" name="Textfeld 24">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F3EEC24-2524-4DF4-B1AD-F79515C600D5}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="16880477" y="8725990"/>
+            <a:ext cx="1766096" cy="299926"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr wrap="square" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle>
+            <a:lvl1pPr marL="0" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="de-DE" sz="1100" i="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:ea typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+                <a:cs typeface="CMU Serif" panose="02000603000000000000" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t>Senkr. Stoß</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="16" name="Freihandform: Form 15">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0273930C-81D6-43A2-810E-78D569EE9C37}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm rot="21311027">
+            <a:off x="18169581" y="8772827"/>
+            <a:ext cx="207429" cy="95571"/>
+          </a:xfrm>
+          <a:custGeom>
+            <a:avLst/>
+            <a:gdLst>
+              <a:gd name="csX0" fmla="*/ 0 w 321013"/>
+              <a:gd name="csY0" fmla="*/ 259404 h 259404"/>
+              <a:gd name="csX1" fmla="*/ 175098 w 321013"/>
+              <a:gd name="csY1" fmla="*/ 201038 h 259404"/>
+              <a:gd name="csX2" fmla="*/ 321013 w 321013"/>
+              <a:gd name="csY2" fmla="*/ 0 h 259404"/>
+            </a:gdLst>
+            <a:ahLst/>
+            <a:cxnLst>
+              <a:cxn ang="0">
+                <a:pos x="csX0" y="csY0"/>
+              </a:cxn>
+              <a:cxn ang="0">
+                <a:pos x="csX1" y="csY1"/>
+              </a:cxn>
+              <a:cxn ang="0">
+                <a:pos x="csX2" y="csY2"/>
+              </a:cxn>
+            </a:cxnLst>
+            <a:rect l="l" t="t" r="r" b="b"/>
+            <a:pathLst>
+              <a:path w="321013" h="259404">
+                <a:moveTo>
+                  <a:pt x="0" y="259404"/>
+                </a:moveTo>
+                <a:cubicBezTo>
+                  <a:pt x="60798" y="251838"/>
+                  <a:pt x="121596" y="244272"/>
+                  <a:pt x="175098" y="201038"/>
+                </a:cubicBezTo>
+                <a:cubicBezTo>
+                  <a:pt x="228600" y="157804"/>
+                  <a:pt x="284805" y="64851"/>
+                  <a:pt x="321013" y="0"/>
+                </a:cubicBezTo>
+              </a:path>
+            </a:pathLst>
+          </a:custGeom>
+          <a:noFill/>
+          <a:ln w="12700" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent5">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="de-DE" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
@@ -22411,19 +26684,19 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="C2" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="B3" s="29"/>
+      <c r="B3" s="30"/>
       <c r="C3" s="6" t="s">
         <v>6</v>
       </c>
@@ -23233,130 +27506,130 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="29"/>
-      <c r="D2" s="31" t="s">
+      <c r="C2" s="30"/>
+      <c r="D2" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32"/>
-      <c r="O2" s="32"/>
-      <c r="P2" s="32"/>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
-      <c r="S2" s="32"/>
-      <c r="T2" s="32"/>
-      <c r="U2" s="32"/>
-      <c r="V2" s="32"/>
-      <c r="W2" s="32"/>
-      <c r="X2" s="32"/>
-      <c r="Y2" s="32"/>
-      <c r="Z2" s="32"/>
-      <c r="AA2" s="32"/>
-      <c r="AB2" s="32"/>
-      <c r="AC2" s="32"/>
-      <c r="AD2" s="32"/>
-      <c r="AE2" s="32"/>
-      <c r="AF2" s="32"/>
-      <c r="AG2" s="32"/>
-      <c r="AH2" s="32"/>
-      <c r="AI2" s="32"/>
-      <c r="AJ2" s="32"/>
-      <c r="AK2" s="32"/>
-      <c r="AL2" s="32"/>
-      <c r="AM2" s="32"/>
-      <c r="AN2" s="32"/>
-      <c r="AO2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
+      <c r="N2" s="33"/>
+      <c r="O2" s="33"/>
+      <c r="P2" s="33"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
+      <c r="T2" s="33"/>
+      <c r="U2" s="33"/>
+      <c r="V2" s="33"/>
+      <c r="W2" s="33"/>
+      <c r="X2" s="33"/>
+      <c r="Y2" s="33"/>
+      <c r="Z2" s="33"/>
+      <c r="AA2" s="33"/>
+      <c r="AB2" s="33"/>
+      <c r="AC2" s="33"/>
+      <c r="AD2" s="33"/>
+      <c r="AE2" s="33"/>
+      <c r="AF2" s="33"/>
+      <c r="AG2" s="33"/>
+      <c r="AH2" s="33"/>
+      <c r="AI2" s="33"/>
+      <c r="AJ2" s="33"/>
+      <c r="AK2" s="33"/>
+      <c r="AL2" s="33"/>
+      <c r="AM2" s="33"/>
+      <c r="AN2" s="33"/>
+      <c r="AO2" s="34"/>
     </row>
     <row r="3" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="30">
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="31">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30">
+      <c r="E3" s="31"/>
+      <c r="F3" s="31">
         <v>1.2</v>
       </c>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30">
+      <c r="G3" s="31"/>
+      <c r="H3" s="31">
         <v>1.3</v>
       </c>
-      <c r="I3" s="30"/>
-      <c r="J3" s="30">
+      <c r="I3" s="31"/>
+      <c r="J3" s="31">
         <v>1.4</v>
       </c>
-      <c r="K3" s="30"/>
-      <c r="L3" s="30">
+      <c r="K3" s="31"/>
+      <c r="L3" s="31">
         <v>1.5</v>
       </c>
-      <c r="M3" s="30"/>
-      <c r="N3" s="30">
+      <c r="M3" s="31"/>
+      <c r="N3" s="31">
         <v>1.6</v>
       </c>
-      <c r="O3" s="30"/>
-      <c r="P3" s="30">
+      <c r="O3" s="31"/>
+      <c r="P3" s="31">
         <v>1.7</v>
       </c>
-      <c r="Q3" s="30"/>
-      <c r="R3" s="30">
+      <c r="Q3" s="31"/>
+      <c r="R3" s="31">
         <v>1.8</v>
       </c>
-      <c r="S3" s="30"/>
-      <c r="T3" s="30">
+      <c r="S3" s="31"/>
+      <c r="T3" s="31">
         <v>1.9</v>
       </c>
-      <c r="U3" s="30"/>
-      <c r="V3" s="30">
+      <c r="U3" s="31"/>
+      <c r="V3" s="31">
         <v>2</v>
       </c>
-      <c r="W3" s="30"/>
-      <c r="X3" s="30">
+      <c r="W3" s="31"/>
+      <c r="X3" s="31">
         <v>2.1</v>
       </c>
-      <c r="Y3" s="30"/>
-      <c r="Z3" s="30">
+      <c r="Y3" s="31"/>
+      <c r="Z3" s="31">
         <v>2.2000000000000002</v>
       </c>
-      <c r="AA3" s="30"/>
-      <c r="AB3" s="30">
+      <c r="AA3" s="31"/>
+      <c r="AB3" s="31">
         <v>2.2999999999999998</v>
       </c>
-      <c r="AC3" s="30"/>
-      <c r="AD3" s="30">
+      <c r="AC3" s="31"/>
+      <c r="AD3" s="31">
         <v>2.4</v>
       </c>
-      <c r="AE3" s="30"/>
-      <c r="AF3" s="30">
+      <c r="AE3" s="31"/>
+      <c r="AF3" s="31">
         <v>3</v>
       </c>
-      <c r="AG3" s="30"/>
-      <c r="AH3" s="30">
+      <c r="AG3" s="31"/>
+      <c r="AH3" s="31">
         <v>4</v>
       </c>
-      <c r="AI3" s="30"/>
-      <c r="AJ3" s="30">
+      <c r="AI3" s="31"/>
+      <c r="AJ3" s="31">
         <v>5</v>
       </c>
-      <c r="AK3" s="30"/>
-      <c r="AL3" s="30">
+      <c r="AK3" s="31"/>
+      <c r="AL3" s="31">
         <v>10</v>
       </c>
-      <c r="AM3" s="30"/>
-      <c r="AN3" s="30">
+      <c r="AM3" s="31"/>
+      <c r="AN3" s="31">
         <v>100000</v>
       </c>
-      <c r="AO3" s="30"/>
+      <c r="AO3" s="31"/>
     </row>
     <row r="4" spans="2:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="11" t="s">
@@ -30816,24 +35089,24 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="29" t="s">
+      <c r="C2" s="36"/>
+      <c r="D2" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B3" s="36"/>
-      <c r="C3" s="37"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="38"/>
       <c r="D3" s="7">
         <v>0</v>
       </c>
@@ -32779,49 +37052,49 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:29" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="44" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="40" t="s">
+      <c r="D2" s="41" t="s">
         <v>2</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="40" t="s">
+      <c r="F2" s="41" t="s">
         <v>2</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="40" t="s">
+      <c r="H2" s="41" t="s">
         <v>2</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="40" t="s">
+      <c r="J2" s="41" t="s">
         <v>2</v>
       </c>
       <c r="K2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="40" t="s">
+      <c r="L2" s="41" t="s">
         <v>2</v>
       </c>
       <c r="M2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="40" t="s">
+      <c r="N2" s="41" t="s">
         <v>2</v>
       </c>
       <c r="O2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="P2" s="40" t="s">
+      <c r="P2" s="41" t="s">
         <v>2</v>
       </c>
       <c r="Q2" s="6" t="s">
@@ -32829,92 +37102,92 @@
       </c>
     </row>
     <row r="3" spans="2:29" x14ac:dyDescent="0.4">
-      <c r="B3" s="44"/>
+      <c r="B3" s="45"/>
       <c r="C3" s="7">
         <v>0</v>
       </c>
-      <c r="D3" s="41"/>
-      <c r="E3" s="38">
+      <c r="D3" s="42"/>
+      <c r="E3" s="39">
         <v>5</v>
       </c>
-      <c r="F3" s="41"/>
-      <c r="G3" s="38">
+      <c r="F3" s="42"/>
+      <c r="G3" s="39">
         <v>10</v>
       </c>
-      <c r="H3" s="41"/>
-      <c r="I3" s="38">
+      <c r="H3" s="42"/>
+      <c r="I3" s="39">
         <v>15</v>
       </c>
-      <c r="J3" s="41"/>
-      <c r="K3" s="38">
+      <c r="J3" s="42"/>
+      <c r="K3" s="39">
         <v>20</v>
       </c>
-      <c r="L3" s="41"/>
-      <c r="M3" s="38">
+      <c r="L3" s="42"/>
+      <c r="M3" s="39">
         <v>25</v>
       </c>
-      <c r="N3" s="41"/>
-      <c r="O3" s="38">
+      <c r="N3" s="42"/>
+      <c r="O3" s="39">
         <v>30</v>
       </c>
-      <c r="P3" s="41"/>
-      <c r="Q3" s="38">
+      <c r="P3" s="42"/>
+      <c r="Q3" s="39">
         <v>35</v>
       </c>
       <c r="AC3"/>
     </row>
     <row r="4" spans="2:29" x14ac:dyDescent="0.4">
-      <c r="B4" s="44"/>
+      <c r="B4" s="45"/>
       <c r="C4" s="8">
         <f>C3*PI()/180</f>
         <v>0</v>
       </c>
-      <c r="D4" s="41"/>
-      <c r="E4" s="39"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="39"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="39"/>
-      <c r="J4" s="41"/>
-      <c r="K4" s="39"/>
-      <c r="L4" s="41"/>
-      <c r="M4" s="39"/>
-      <c r="N4" s="41"/>
-      <c r="O4" s="39"/>
-      <c r="P4" s="41"/>
-      <c r="Q4" s="39"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="42"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="42"/>
+      <c r="K4" s="40"/>
+      <c r="L4" s="42"/>
+      <c r="M4" s="40"/>
+      <c r="N4" s="42"/>
+      <c r="O4" s="40"/>
+      <c r="P4" s="42"/>
+      <c r="Q4" s="40"/>
     </row>
     <row r="5" spans="2:29" x14ac:dyDescent="0.4">
-      <c r="B5" s="45"/>
+      <c r="B5" s="46"/>
       <c r="C5" s="14">
         <f>PI()/2</f>
         <v>1.5707963267948966</v>
       </c>
-      <c r="D5" s="42"/>
+      <c r="D5" s="43"/>
       <c r="E5" s="15">
         <v>1.5</v>
       </c>
-      <c r="F5" s="42"/>
+      <c r="F5" s="43"/>
       <c r="G5" s="15">
         <v>1.46</v>
       </c>
-      <c r="H5" s="42"/>
+      <c r="H5" s="43"/>
       <c r="I5" s="15">
         <v>1.42</v>
       </c>
-      <c r="J5" s="42"/>
+      <c r="J5" s="43"/>
       <c r="K5" s="23">
         <v>1.39</v>
       </c>
-      <c r="L5" s="42"/>
+      <c r="L5" s="43"/>
       <c r="M5" s="23">
         <v>1.36</v>
       </c>
-      <c r="N5" s="42"/>
+      <c r="N5" s="43"/>
       <c r="O5" s="23">
         <v>1.32</v>
       </c>
-      <c r="P5" s="42"/>
+      <c r="P5" s="43"/>
       <c r="Q5" s="23">
         <v>1.26</v>
       </c>
@@ -34961,4 +39234,1567 @@
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDA1DE34-B1B3-4D4C-92A2-DA5E0EED9EFA}">
+  <dimension ref="B2:R55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="15.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
+    <col min="2" max="3" width="13.88671875" style="24" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" style="1" customWidth="1"/>
+    <col min="5" max="7" width="13.88671875" style="24" customWidth="1"/>
+    <col min="8" max="9" width="13.88671875" style="1" customWidth="1"/>
+    <col min="10" max="11" width="13.88671875" style="24" customWidth="1"/>
+    <col min="12" max="13" width="13.88671875" style="1" customWidth="1"/>
+    <col min="14" max="15" width="13.88671875" style="24" customWidth="1"/>
+    <col min="16" max="17" width="13.88671875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="13.88671875" style="24" customWidth="1"/>
+    <col min="19" max="19" width="2.6640625" style="1" customWidth="1"/>
+    <col min="20" max="16384" width="11.5546875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:18" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B2" s="41" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="30"/>
+      <c r="O2" s="30"/>
+      <c r="P2" s="30"/>
+      <c r="Q2" s="30"/>
+      <c r="R2" s="30"/>
+    </row>
+    <row r="3" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B3" s="42"/>
+      <c r="C3" s="47">
+        <v>0</v>
+      </c>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47">
+        <v>5</v>
+      </c>
+      <c r="F3" s="47"/>
+      <c r="G3" s="48">
+        <v>10</v>
+      </c>
+      <c r="H3" s="49"/>
+      <c r="I3" s="48">
+        <v>15</v>
+      </c>
+      <c r="J3" s="49"/>
+      <c r="K3" s="48">
+        <v>20</v>
+      </c>
+      <c r="L3" s="49"/>
+      <c r="M3" s="48">
+        <v>25</v>
+      </c>
+      <c r="N3" s="49"/>
+      <c r="O3" s="48">
+        <v>30</v>
+      </c>
+      <c r="P3" s="49"/>
+      <c r="Q3" s="48">
+        <v>35</v>
+      </c>
+      <c r="R3" s="49"/>
+    </row>
+    <row r="4" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B4" s="43"/>
+      <c r="C4" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K4" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M4" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="N4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="O4" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="P4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q4" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="R4" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B5" s="10">
+        <v>1</v>
+      </c>
+      <c r="C5" s="26">
+        <v>1</v>
+      </c>
+      <c r="D5" s="26">
+        <v>1</v>
+      </c>
+      <c r="E5" s="10">
+        <v>3.5</v>
+      </c>
+      <c r="F5" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="G5" s="10">
+        <v>3.5</v>
+      </c>
+      <c r="H5" s="3">
+        <v>2.9049999999999998</v>
+      </c>
+      <c r="I5" s="10">
+        <v>3.5</v>
+      </c>
+      <c r="J5" s="3">
+        <v>2.61</v>
+      </c>
+      <c r="K5" s="10">
+        <v>3.5</v>
+      </c>
+      <c r="L5" s="3">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="M5" s="10">
+        <v>3.5</v>
+      </c>
+      <c r="N5" s="3">
+        <v>1.9830000000000001</v>
+      </c>
+      <c r="O5" s="10">
+        <v>3.5</v>
+      </c>
+      <c r="P5" s="3">
+        <v>1.657</v>
+      </c>
+      <c r="Q5" s="10">
+        <v>3.5</v>
+      </c>
+      <c r="R5" s="3">
+        <v>1.268</v>
+      </c>
+    </row>
+    <row r="6" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B6" s="10">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C6" s="10">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0.91</v>
+      </c>
+      <c r="E6" s="10">
+        <v>3</v>
+      </c>
+      <c r="F6" s="3">
+        <v>2.75</v>
+      </c>
+      <c r="G6" s="10">
+        <v>3</v>
+      </c>
+      <c r="H6" s="3">
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="I6" s="10">
+        <v>3</v>
+      </c>
+      <c r="J6" s="3">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="K6" s="10">
+        <v>3</v>
+      </c>
+      <c r="L6" s="3">
+        <v>1.9930000000000001</v>
+      </c>
+      <c r="M6" s="10">
+        <v>3.2</v>
+      </c>
+      <c r="N6" s="3">
+        <v>1.83</v>
+      </c>
+      <c r="O6" s="10">
+        <v>3.2</v>
+      </c>
+      <c r="P6" s="3">
+        <v>1.516</v>
+      </c>
+      <c r="Q6" s="10">
+        <v>3.3</v>
+      </c>
+      <c r="R6" s="3">
+        <v>1.1559999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B7" s="10">
+        <v>1.2</v>
+      </c>
+      <c r="C7" s="10">
+        <v>1.2</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0.84199999999999997</v>
+      </c>
+      <c r="E7" s="10">
+        <v>2.5</v>
+      </c>
+      <c r="F7" s="3">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G7" s="10">
+        <v>2.5</v>
+      </c>
+      <c r="H7" s="3">
+        <v>2.0880000000000001</v>
+      </c>
+      <c r="I7" s="10">
+        <v>2.5</v>
+      </c>
+      <c r="J7" s="3">
+        <v>1.875</v>
+      </c>
+      <c r="K7" s="10">
+        <v>2.5</v>
+      </c>
+      <c r="L7" s="3">
+        <v>1.6479999999999999</v>
+      </c>
+      <c r="M7" s="10">
+        <v>2.9</v>
+      </c>
+      <c r="N7" s="3">
+        <v>1.66</v>
+      </c>
+      <c r="O7" s="10">
+        <v>2.9</v>
+      </c>
+      <c r="P7" s="3">
+        <v>1.3460000000000001</v>
+      </c>
+      <c r="Q7" s="10">
+        <v>3.2</v>
+      </c>
+      <c r="R7" s="3">
+        <v>1.073</v>
+      </c>
+    </row>
+    <row r="8" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B8" s="10">
+        <v>1.3</v>
+      </c>
+      <c r="C8" s="10">
+        <v>1.3</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0.78600000000000003</v>
+      </c>
+      <c r="E8" s="10">
+        <v>2</v>
+      </c>
+      <c r="F8" s="3">
+        <v>1.825</v>
+      </c>
+      <c r="G8" s="10">
+        <v>2</v>
+      </c>
+      <c r="H8" s="3">
+        <v>1.6439999999999999</v>
+      </c>
+      <c r="I8" s="10">
+        <v>2</v>
+      </c>
+      <c r="J8" s="3">
+        <v>1.45</v>
+      </c>
+      <c r="K8" s="10">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="L8" s="3">
+        <v>1.4059999999999999</v>
+      </c>
+      <c r="M8" s="10">
+        <v>2.6</v>
+      </c>
+      <c r="N8" s="3">
+        <v>1.4650000000000001</v>
+      </c>
+      <c r="O8" s="10">
+        <v>2.7</v>
+      </c>
+      <c r="P8" s="3">
+        <v>1.21</v>
+      </c>
+      <c r="Q8" s="26">
+        <v>3.1440000000000001</v>
+      </c>
+      <c r="R8" s="26">
+        <v>0.95699999999999996</v>
+      </c>
+    </row>
+    <row r="9" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B9" s="10">
+        <v>1.4</v>
+      </c>
+      <c r="C9" s="10">
+        <v>1.4</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0.74</v>
+      </c>
+      <c r="E9" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="F9" s="3">
+        <v>1.327</v>
+      </c>
+      <c r="G9" s="10">
+        <v>1.7</v>
+      </c>
+      <c r="H9" s="3">
+        <v>1.35</v>
+      </c>
+      <c r="I9" s="10">
+        <v>1.9</v>
+      </c>
+      <c r="J9" s="3">
+        <v>1.35</v>
+      </c>
+      <c r="K9" s="10">
+        <v>2</v>
+      </c>
+      <c r="L9" s="3">
+        <v>1.21</v>
+      </c>
+      <c r="M9" s="10">
+        <v>2.4</v>
+      </c>
+      <c r="N9" s="3">
+        <v>1.31</v>
+      </c>
+      <c r="O9" s="10">
+        <v>2.6</v>
+      </c>
+      <c r="P9" s="3">
+        <v>1.1180000000000001</v>
+      </c>
+      <c r="Q9" s="10">
+        <v>3.2</v>
+      </c>
+      <c r="R9" s="3">
+        <v>0.86199999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B10" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="C10" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0.70199999999999996</v>
+      </c>
+      <c r="E10" s="10">
+        <v>1.4</v>
+      </c>
+      <c r="F10" s="3">
+        <v>1.22</v>
+      </c>
+      <c r="G10" s="10">
+        <v>1.6</v>
+      </c>
+      <c r="H10" s="3">
+        <v>1.24</v>
+      </c>
+      <c r="I10" s="10">
+        <v>1.8</v>
+      </c>
+      <c r="J10" s="3">
+        <v>1.2490000000000001</v>
+      </c>
+      <c r="K10" s="10">
+        <v>1.9</v>
+      </c>
+      <c r="L10" s="50">
+        <v>1.083</v>
+      </c>
+      <c r="M10" s="10">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="N10" s="3">
+        <v>1.1120000000000001</v>
+      </c>
+      <c r="O10" s="26">
+        <v>2.52</v>
+      </c>
+      <c r="P10" s="26">
+        <v>0.94499999999999995</v>
+      </c>
+      <c r="Q10" s="10">
+        <v>3.3</v>
+      </c>
+      <c r="R10" s="3">
+        <v>0.81200000000000006</v>
+      </c>
+    </row>
+    <row r="11" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B11" s="10">
+        <v>1.6</v>
+      </c>
+      <c r="C11" s="10">
+        <v>1.6</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0.66800000000000004</v>
+      </c>
+      <c r="E11" s="10">
+        <v>1.3</v>
+      </c>
+      <c r="F11" s="3">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="G11" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="H11" s="3">
+        <v>1.1180000000000001</v>
+      </c>
+      <c r="I11" s="10">
+        <v>1.7</v>
+      </c>
+      <c r="J11" s="3">
+        <v>1.123</v>
+      </c>
+      <c r="K11" s="26">
+        <v>1.84</v>
+      </c>
+      <c r="L11" s="26">
+        <v>0.91400000000000003</v>
+      </c>
+      <c r="M11" s="26">
+        <v>2.125</v>
+      </c>
+      <c r="N11" s="26">
+        <v>0.93</v>
+      </c>
+      <c r="O11" s="10">
+        <v>2.6</v>
+      </c>
+      <c r="P11" s="3">
+        <v>0.81200000000000006</v>
+      </c>
+      <c r="Q11" s="10">
+        <v>3.5</v>
+      </c>
+      <c r="R11" s="3">
+        <v>0.753</v>
+      </c>
+    </row>
+    <row r="12" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B12" s="10">
+        <v>1.7</v>
+      </c>
+      <c r="C12" s="10">
+        <v>1.8</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0.61599999999999999</v>
+      </c>
+      <c r="E12" s="26">
+        <v>1.24</v>
+      </c>
+      <c r="F12" s="26">
+        <v>0.95</v>
+      </c>
+      <c r="G12" s="26">
+        <v>1.42</v>
+      </c>
+      <c r="H12" s="26">
+        <v>0.92400000000000004</v>
+      </c>
+      <c r="I12" s="26">
+        <v>1.6120000000000001</v>
+      </c>
+      <c r="J12" s="26">
+        <v>0.92500000000000004</v>
+      </c>
+      <c r="K12" s="10">
+        <v>1.9</v>
+      </c>
+      <c r="L12" s="3">
+        <v>0.78800000000000003</v>
+      </c>
+      <c r="M12" s="10">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="N12" s="50">
+        <v>0.79600000000000004</v>
+      </c>
+      <c r="O12" s="10">
+        <v>2.7</v>
+      </c>
+      <c r="P12" s="50">
+        <v>0.75800000000000001</v>
+      </c>
+      <c r="Q12" s="10"/>
+      <c r="R12" s="50"/>
+    </row>
+    <row r="13" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B13" s="10">
+        <v>1.8</v>
+      </c>
+      <c r="C13" s="10">
+        <v>2</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0.57799999999999996</v>
+      </c>
+      <c r="E13" s="10">
+        <v>1.3</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0.83299999999999996</v>
+      </c>
+      <c r="G13" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="H13" s="3">
+        <v>0.78500000000000003</v>
+      </c>
+      <c r="I13" s="10">
+        <v>1.7</v>
+      </c>
+      <c r="J13" s="50">
+        <v>0.77</v>
+      </c>
+      <c r="K13" s="10">
+        <v>2</v>
+      </c>
+      <c r="L13" s="3">
+        <v>0.73</v>
+      </c>
+      <c r="M13" s="10">
+        <v>2.4</v>
+      </c>
+      <c r="N13" s="50">
+        <v>0.69799999999999995</v>
+      </c>
+      <c r="O13" s="10">
+        <v>2.9</v>
+      </c>
+      <c r="P13" s="50">
+        <v>0.69599999999999995</v>
+      </c>
+      <c r="Q13" s="10"/>
+      <c r="R13" s="50"/>
+    </row>
+    <row r="14" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B14" s="10">
+        <v>1.9</v>
+      </c>
+      <c r="C14" s="10">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0.54800000000000004</v>
+      </c>
+      <c r="E14" s="10">
+        <v>1.4</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0.76500000000000001</v>
+      </c>
+      <c r="G14" s="10">
+        <v>1.6</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0.72399999999999998</v>
+      </c>
+      <c r="I14" s="10">
+        <v>1.8</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0.71199999999999997</v>
+      </c>
+      <c r="K14" s="10">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="L14" s="50">
+        <v>0.65600000000000003</v>
+      </c>
+      <c r="M14" s="10">
+        <v>2.6</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0.65</v>
+      </c>
+      <c r="O14" s="10">
+        <v>3.2</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0.64500000000000002</v>
+      </c>
+      <c r="Q14" s="10"/>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B15" s="10">
+        <v>2</v>
+      </c>
+      <c r="C15" s="10">
+        <v>2.4</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E15" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0.72</v>
+      </c>
+      <c r="G15" s="10">
+        <v>1.7</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0.68600000000000005</v>
+      </c>
+      <c r="I15" s="10">
+        <v>2</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0.64400000000000002</v>
+      </c>
+      <c r="K15" s="10">
+        <v>2.5</v>
+      </c>
+      <c r="L15" s="3">
+        <v>0.59599999999999997</v>
+      </c>
+      <c r="M15" s="10">
+        <v>2.9</v>
+      </c>
+      <c r="N15" s="3">
+        <v>0.60499999999999998</v>
+      </c>
+      <c r="O15" s="10">
+        <v>3.5</v>
+      </c>
+      <c r="P15" s="3">
+        <v>0.61199999999999999</v>
+      </c>
+      <c r="Q15" s="10"/>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B16" s="10">
+        <v>2.1</v>
+      </c>
+      <c r="C16" s="10">
+        <v>2.63</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="10">
+        <v>1.6</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0.68300000000000005</v>
+      </c>
+      <c r="G16" s="10">
+        <v>2</v>
+      </c>
+      <c r="H16" s="3">
+        <v>0.60399999999999998</v>
+      </c>
+      <c r="I16" s="10">
+        <v>2.6</v>
+      </c>
+      <c r="J16" s="3">
+        <v>0.54800000000000004</v>
+      </c>
+      <c r="K16" s="10">
+        <v>3</v>
+      </c>
+      <c r="L16" s="3">
+        <v>0.54200000000000004</v>
+      </c>
+      <c r="M16" s="10">
+        <v>3.2</v>
+      </c>
+      <c r="N16" s="3">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="O16" s="10"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="10"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B17" s="10">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C17" s="10"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="10">
+        <v>1.7</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0.65200000000000002</v>
+      </c>
+      <c r="G17" s="10">
+        <v>2.5</v>
+      </c>
+      <c r="H17" s="3">
+        <v>0.53500000000000003</v>
+      </c>
+      <c r="I17" s="10">
+        <v>3.1120000000000001</v>
+      </c>
+      <c r="J17" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="K17" s="10">
+        <v>3.5</v>
+      </c>
+      <c r="L17" s="3">
+        <v>0.51200000000000001</v>
+      </c>
+      <c r="M17" s="10">
+        <v>3.5</v>
+      </c>
+      <c r="N17" s="3">
+        <v>0.54900000000000004</v>
+      </c>
+      <c r="O17" s="10"/>
+      <c r="P17" s="3"/>
+      <c r="Q17" s="10"/>
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B18" s="10">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="C18" s="10"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="10">
+        <v>2</v>
+      </c>
+      <c r="F18" s="3">
+        <v>0.58499999999999996</v>
+      </c>
+      <c r="G18" s="10">
+        <v>2.8250000000000002</v>
+      </c>
+      <c r="H18" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="I18" s="10"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="3"/>
+      <c r="O18" s="10"/>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="10"/>
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B19" s="10">
+        <v>2.4</v>
+      </c>
+      <c r="C19" s="10"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="10">
+        <v>2.5</v>
+      </c>
+      <c r="F19" s="3">
+        <v>0.52</v>
+      </c>
+      <c r="G19" s="10"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="10"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="10"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="10"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="10"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B20" s="10">
+        <v>2.5</v>
+      </c>
+      <c r="C20" s="10"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="10">
+        <v>2.67</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="G20" s="10"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="3"/>
+      <c r="O20" s="10"/>
+      <c r="P20" s="3"/>
+      <c r="Q20" s="10"/>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B21" s="10">
+        <v>2.6</v>
+      </c>
+      <c r="C21" s="10"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="3"/>
+      <c r="O21" s="10"/>
+      <c r="P21" s="3"/>
+      <c r="Q21" s="10"/>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B22" s="10">
+        <v>2.7</v>
+      </c>
+      <c r="C22" s="10"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="3"/>
+      <c r="O22" s="10"/>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="10"/>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B23" s="10">
+        <v>2.8</v>
+      </c>
+      <c r="C23" s="10"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="10"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="10"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="10"/>
+      <c r="P23" s="3"/>
+      <c r="Q23" s="10"/>
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B24" s="10">
+        <v>2.9</v>
+      </c>
+      <c r="C24" s="10"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="10"/>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="10"/>
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B25" s="10">
+        <v>3</v>
+      </c>
+      <c r="C25" s="10"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="10"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="10"/>
+      <c r="N25" s="3"/>
+      <c r="O25" s="10"/>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="10"/>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B26" s="10">
+        <v>3.1</v>
+      </c>
+      <c r="C26" s="10"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="10"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="10"/>
+      <c r="L26" s="3"/>
+      <c r="M26" s="10"/>
+      <c r="N26" s="3"/>
+      <c r="O26" s="10"/>
+      <c r="P26" s="3"/>
+      <c r="Q26" s="10"/>
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B27" s="10">
+        <v>3.2</v>
+      </c>
+      <c r="C27" s="10"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="3"/>
+      <c r="M27" s="10"/>
+      <c r="N27" s="3"/>
+      <c r="O27" s="10"/>
+      <c r="P27" s="3"/>
+      <c r="Q27" s="10"/>
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B28" s="10">
+        <v>3.3</v>
+      </c>
+      <c r="C28" s="10"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="3"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="3"/>
+      <c r="O28" s="10"/>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="10"/>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B29" s="10">
+        <v>3.4</v>
+      </c>
+      <c r="C29" s="10"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="10"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="10"/>
+      <c r="L29" s="3"/>
+      <c r="M29" s="10"/>
+      <c r="N29" s="3"/>
+      <c r="O29" s="10"/>
+      <c r="P29" s="3"/>
+      <c r="Q29" s="10"/>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B30" s="10">
+        <v>3.5</v>
+      </c>
+      <c r="C30" s="10"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="10"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="10"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="10"/>
+      <c r="N30" s="3"/>
+      <c r="O30" s="10"/>
+      <c r="P30" s="3"/>
+      <c r="Q30" s="10"/>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B31"/>
+      <c r="C31"/>
+      <c r="D31"/>
+      <c r="E31"/>
+      <c r="F31"/>
+      <c r="G31"/>
+      <c r="H31"/>
+      <c r="I31"/>
+      <c r="J31"/>
+      <c r="K31"/>
+      <c r="L31"/>
+      <c r="M31"/>
+      <c r="N31"/>
+      <c r="O31"/>
+      <c r="P31"/>
+      <c r="Q31"/>
+      <c r="R31"/>
+    </row>
+    <row r="32" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B32"/>
+      <c r="C32"/>
+      <c r="D32"/>
+      <c r="E32"/>
+      <c r="F32"/>
+      <c r="G32"/>
+      <c r="H32"/>
+      <c r="I32"/>
+      <c r="J32"/>
+      <c r="K32"/>
+      <c r="L32"/>
+      <c r="M32"/>
+      <c r="N32"/>
+      <c r="O32"/>
+      <c r="P32"/>
+      <c r="Q32"/>
+      <c r="R32"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B33"/>
+      <c r="C33"/>
+      <c r="D33"/>
+      <c r="E33"/>
+      <c r="F33"/>
+      <c r="G33"/>
+      <c r="H33"/>
+      <c r="I33"/>
+      <c r="J33"/>
+      <c r="K33"/>
+      <c r="L33"/>
+      <c r="M33"/>
+      <c r="N33"/>
+      <c r="O33"/>
+      <c r="P33"/>
+      <c r="Q33"/>
+      <c r="R33"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B34"/>
+      <c r="C34"/>
+      <c r="D34"/>
+      <c r="E34"/>
+      <c r="F34"/>
+      <c r="G34"/>
+      <c r="H34"/>
+      <c r="I34"/>
+      <c r="J34"/>
+      <c r="K34"/>
+      <c r="L34"/>
+      <c r="M34"/>
+      <c r="N34"/>
+      <c r="O34"/>
+      <c r="P34"/>
+      <c r="Q34"/>
+      <c r="R34"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B35"/>
+      <c r="C35"/>
+      <c r="D35"/>
+      <c r="E35"/>
+      <c r="F35"/>
+      <c r="G35"/>
+      <c r="H35"/>
+      <c r="I35"/>
+      <c r="J35"/>
+      <c r="K35"/>
+      <c r="L35"/>
+      <c r="M35"/>
+      <c r="N35"/>
+      <c r="O35"/>
+      <c r="P35"/>
+      <c r="Q35"/>
+      <c r="R35"/>
+    </row>
+    <row r="36" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B36"/>
+      <c r="C36"/>
+      <c r="D36"/>
+      <c r="E36"/>
+      <c r="F36"/>
+      <c r="G36"/>
+      <c r="H36"/>
+      <c r="I36"/>
+      <c r="J36"/>
+      <c r="K36"/>
+      <c r="L36"/>
+      <c r="M36"/>
+      <c r="N36"/>
+      <c r="O36"/>
+      <c r="P36"/>
+      <c r="Q36"/>
+      <c r="R36"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B37"/>
+      <c r="C37"/>
+      <c r="D37"/>
+      <c r="E37"/>
+      <c r="F37"/>
+      <c r="G37"/>
+      <c r="H37"/>
+      <c r="I37"/>
+      <c r="J37"/>
+      <c r="K37"/>
+      <c r="L37"/>
+      <c r="M37"/>
+      <c r="N37"/>
+      <c r="O37"/>
+      <c r="P37"/>
+      <c r="Q37"/>
+      <c r="R37"/>
+    </row>
+    <row r="38" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B38"/>
+      <c r="C38"/>
+      <c r="D38"/>
+      <c r="E38"/>
+      <c r="F38"/>
+      <c r="G38"/>
+      <c r="H38"/>
+      <c r="I38"/>
+      <c r="J38"/>
+      <c r="K38"/>
+      <c r="L38"/>
+      <c r="M38"/>
+      <c r="N38"/>
+      <c r="O38"/>
+      <c r="P38"/>
+      <c r="Q38"/>
+      <c r="R38"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B39"/>
+      <c r="C39"/>
+      <c r="D39"/>
+      <c r="E39"/>
+      <c r="F39"/>
+      <c r="G39"/>
+      <c r="H39"/>
+      <c r="I39"/>
+      <c r="J39"/>
+      <c r="K39"/>
+      <c r="L39"/>
+      <c r="M39"/>
+      <c r="N39"/>
+      <c r="O39"/>
+      <c r="P39"/>
+      <c r="Q39"/>
+      <c r="R39"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B40"/>
+      <c r="C40"/>
+      <c r="D40"/>
+      <c r="E40"/>
+      <c r="F40"/>
+      <c r="G40"/>
+      <c r="H40"/>
+      <c r="I40"/>
+      <c r="J40"/>
+      <c r="K40"/>
+      <c r="L40"/>
+      <c r="M40"/>
+      <c r="N40"/>
+      <c r="O40"/>
+      <c r="P40"/>
+      <c r="Q40"/>
+      <c r="R40"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B41"/>
+      <c r="C41"/>
+      <c r="D41"/>
+      <c r="E41"/>
+      <c r="F41"/>
+      <c r="G41"/>
+      <c r="H41"/>
+      <c r="I41"/>
+      <c r="J41"/>
+      <c r="K41"/>
+      <c r="L41"/>
+      <c r="M41"/>
+      <c r="N41"/>
+      <c r="O41"/>
+      <c r="P41"/>
+      <c r="Q41"/>
+      <c r="R41"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B42"/>
+      <c r="C42"/>
+      <c r="D42"/>
+      <c r="E42"/>
+      <c r="F42"/>
+      <c r="G42"/>
+      <c r="H42"/>
+      <c r="I42"/>
+      <c r="J42"/>
+      <c r="K42"/>
+      <c r="L42"/>
+      <c r="M42"/>
+      <c r="N42"/>
+      <c r="O42"/>
+      <c r="P42"/>
+      <c r="Q42"/>
+      <c r="R42"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B43"/>
+      <c r="C43"/>
+      <c r="D43"/>
+      <c r="E43"/>
+      <c r="F43"/>
+      <c r="G43"/>
+      <c r="H43"/>
+      <c r="I43"/>
+      <c r="J43"/>
+      <c r="K43"/>
+      <c r="L43"/>
+      <c r="M43"/>
+      <c r="N43"/>
+      <c r="O43"/>
+      <c r="P43"/>
+      <c r="Q43"/>
+      <c r="R43"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B44"/>
+      <c r="C44"/>
+      <c r="D44"/>
+      <c r="E44"/>
+      <c r="F44"/>
+      <c r="G44"/>
+      <c r="H44"/>
+      <c r="I44"/>
+      <c r="J44"/>
+      <c r="K44"/>
+      <c r="L44"/>
+      <c r="M44"/>
+      <c r="N44"/>
+      <c r="O44"/>
+      <c r="P44"/>
+      <c r="Q44"/>
+      <c r="R44"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B45"/>
+      <c r="C45"/>
+      <c r="D45"/>
+      <c r="E45"/>
+      <c r="F45"/>
+      <c r="G45"/>
+      <c r="H45"/>
+      <c r="I45"/>
+      <c r="J45"/>
+      <c r="K45"/>
+      <c r="L45"/>
+      <c r="M45"/>
+      <c r="N45"/>
+      <c r="O45"/>
+      <c r="P45"/>
+      <c r="Q45"/>
+      <c r="R45"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B46"/>
+      <c r="C46"/>
+      <c r="D46"/>
+      <c r="E46"/>
+      <c r="F46"/>
+      <c r="G46"/>
+      <c r="H46"/>
+      <c r="I46"/>
+      <c r="J46"/>
+      <c r="K46"/>
+      <c r="L46"/>
+      <c r="M46"/>
+      <c r="N46"/>
+      <c r="O46"/>
+      <c r="P46"/>
+      <c r="Q46"/>
+      <c r="R46"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B47"/>
+      <c r="C47"/>
+      <c r="D47"/>
+      <c r="E47"/>
+      <c r="F47"/>
+      <c r="G47"/>
+      <c r="H47"/>
+      <c r="I47"/>
+      <c r="J47"/>
+      <c r="K47"/>
+      <c r="L47"/>
+      <c r="M47"/>
+      <c r="N47"/>
+      <c r="O47"/>
+      <c r="P47"/>
+      <c r="Q47"/>
+      <c r="R47"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B48"/>
+      <c r="C48"/>
+      <c r="D48"/>
+      <c r="E48"/>
+      <c r="F48"/>
+      <c r="G48"/>
+      <c r="H48"/>
+      <c r="I48"/>
+      <c r="J48"/>
+      <c r="K48"/>
+      <c r="L48"/>
+      <c r="M48"/>
+      <c r="N48"/>
+      <c r="O48"/>
+      <c r="P48"/>
+      <c r="Q48"/>
+      <c r="R48"/>
+    </row>
+    <row r="49" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B49"/>
+      <c r="C49"/>
+      <c r="D49"/>
+      <c r="E49"/>
+      <c r="F49"/>
+      <c r="G49"/>
+      <c r="H49"/>
+      <c r="I49"/>
+      <c r="J49"/>
+      <c r="K49"/>
+      <c r="L49"/>
+      <c r="M49"/>
+      <c r="N49"/>
+      <c r="O49"/>
+      <c r="P49"/>
+      <c r="Q49"/>
+      <c r="R49"/>
+    </row>
+    <row r="50" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B50"/>
+      <c r="C50"/>
+      <c r="D50"/>
+      <c r="E50"/>
+      <c r="F50"/>
+      <c r="G50"/>
+      <c r="H50"/>
+      <c r="I50"/>
+      <c r="J50"/>
+      <c r="K50"/>
+      <c r="L50"/>
+      <c r="M50"/>
+      <c r="N50"/>
+      <c r="O50"/>
+      <c r="P50"/>
+      <c r="Q50"/>
+      <c r="R50"/>
+    </row>
+    <row r="51" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B51"/>
+      <c r="C51"/>
+      <c r="D51"/>
+      <c r="E51"/>
+      <c r="F51"/>
+      <c r="G51"/>
+      <c r="H51"/>
+      <c r="I51"/>
+      <c r="J51"/>
+      <c r="K51"/>
+      <c r="L51"/>
+      <c r="M51"/>
+      <c r="N51"/>
+      <c r="O51"/>
+      <c r="P51"/>
+      <c r="Q51"/>
+      <c r="R51"/>
+    </row>
+    <row r="52" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B52"/>
+      <c r="C52"/>
+      <c r="D52"/>
+      <c r="E52"/>
+      <c r="F52"/>
+      <c r="G52"/>
+      <c r="H52"/>
+      <c r="I52"/>
+      <c r="J52"/>
+      <c r="K52"/>
+      <c r="L52"/>
+      <c r="M52"/>
+      <c r="N52"/>
+      <c r="O52"/>
+      <c r="P52"/>
+      <c r="Q52"/>
+      <c r="R52"/>
+    </row>
+    <row r="53" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B53"/>
+      <c r="C53"/>
+      <c r="D53"/>
+      <c r="E53"/>
+      <c r="F53"/>
+      <c r="G53"/>
+      <c r="H53"/>
+      <c r="I53"/>
+      <c r="J53"/>
+      <c r="K53"/>
+      <c r="L53"/>
+      <c r="M53"/>
+      <c r="N53"/>
+      <c r="O53"/>
+      <c r="P53"/>
+      <c r="Q53"/>
+      <c r="R53"/>
+    </row>
+    <row r="54" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B54"/>
+      <c r="C54"/>
+      <c r="D54"/>
+      <c r="E54"/>
+      <c r="F54"/>
+      <c r="G54"/>
+      <c r="H54"/>
+      <c r="I54"/>
+      <c r="J54"/>
+      <c r="K54"/>
+      <c r="L54"/>
+      <c r="M54"/>
+      <c r="N54"/>
+      <c r="O54"/>
+      <c r="P54"/>
+      <c r="Q54"/>
+      <c r="R54"/>
+    </row>
+    <row r="55" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B55"/>
+      <c r="C55"/>
+      <c r="D55"/>
+      <c r="E55"/>
+      <c r="F55"/>
+      <c r="G55"/>
+      <c r="H55"/>
+      <c r="I55"/>
+      <c r="J55"/>
+      <c r="K55"/>
+      <c r="L55"/>
+      <c r="M55"/>
+      <c r="N55"/>
+      <c r="O55"/>
+      <c r="P55"/>
+      <c r="Q55"/>
+      <c r="R55"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="C2:R2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="K3:L3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>